--- a/00.test_case/Demoblaze_TestCases_Login_Cart.xlsx
+++ b/00.test_case/Demoblaze_TestCases_Login_Cart.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="370">
   <si>
     <t xml:space="preserve">Demoblaze – Test Case Suite (Login, Cart &amp; Order)</t>
   </si>
@@ -508,7 +508,7 @@
     <t xml:space="preserve">Input treated as empty: validation alert shown, no login request is accepted; user not logged in</t>
   </si>
   <si>
-    <t xml:space="preserve">Confirm trimming rule with BA</t>
+    <t xml:space="preserve">Alert 'Wrong password.' shown; whitespace input is sent to the API and an account with a whitespace-only username exists</t>
   </si>
   <si>
     <t>LG-017</t>
@@ -568,6 +568,9 @@
     <t xml:space="preserve">System applies one consistent rule: either input is trimmed and login succeeds, or login fails with an error alert. No partial/broken session</t>
   </si>
   <si>
+    <t xml:space="preserve">Confirm trimming rule with BA</t>
+  </si>
+  <si>
     <t>LG-020</t>
   </si>
   <si>
@@ -592,7 +595,7 @@
     <t>LG-021</t>
   </si>
   <si>
-    <t xml:space="preserve">Very long username (300 characters)</t>
+    <t xml:space="preserve">Very long username (2000 characters)</t>
   </si>
   <si>
     <t xml:space="preserve">Username: 'a' x 300
@@ -605,6 +608,9 @@
   </si>
   <si>
     <t xml:space="preserve">Error alert shown; page remains responsive; no server error</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No alert is shown, the Log in modal stays open and the user gets no feedback.</t>
   </si>
   <si>
     <t>LG-022</t>
@@ -1274,7 +1280,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11.000000"/>
       <color theme="1"/>
@@ -1305,6 +1311,11 @@
       <b/>
       <sz val="11.000000"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="9.000000"/>
+      <color rgb="FF8C8C8C"/>
+      <name val="Courier New"/>
     </font>
   </fonts>
   <fills count="6">
@@ -1371,7 +1382,7 @@
     <xf fontId="1" fillId="0" borderId="0" numFmtId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" quotePrefix="0" pivotButton="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" quotePrefix="0" pivotButton="0"/>
     <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" quotePrefix="0" pivotButton="0"/>
@@ -1406,6 +1417,9 @@
     </xf>
     <xf fontId="1" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="6" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -2085,11 +2099,11 @@
       </c>
       <c r="B18" s="7">
         <f>COUNTIF(Login!$M:$M,"Pass")</f>
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="C18" s="7">
         <f>COUNTIF(Login!$M:$M,"Fail")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D18" s="7">
         <f>COUNTIF(Login!$M:$M,"Blocked")</f>
@@ -2097,11 +2111,11 @@
       </c>
       <c r="E18" s="7">
         <f>COUNTIF(Login!$M:$M,"Not Run")</f>
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="F18" s="11">
         <f t="shared" ref="F18:F20" si="1">IFERROR(B18/(B18+C18+D18),0)</f>
-        <v>1</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
@@ -2204,7 +2218,7 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" style="1" width="10"/>
     <col customWidth="1" min="2" max="2" style="1" width="9"/>
@@ -2435,7 +2449,7 @@
         <v>72</v>
       </c>
       <c r="M5" s="13" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N5" s="13"/>
       <c r="O5" s="13"/>
@@ -2478,7 +2492,7 @@
         <v>72</v>
       </c>
       <c r="M6" s="13" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N6" s="13"/>
       <c r="O6" s="13"/>
@@ -2521,7 +2535,7 @@
         <v>56</v>
       </c>
       <c r="M7" s="13" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N7" s="13"/>
       <c r="O7" s="13"/>
@@ -2564,7 +2578,7 @@
         <v>56</v>
       </c>
       <c r="M8" s="13" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N8" s="13"/>
       <c r="O8" s="13"/>
@@ -2607,7 +2621,7 @@
         <v>65</v>
       </c>
       <c r="M9" s="13" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N9" s="13"/>
       <c r="O9" s="13" t="s">
@@ -2652,7 +2666,7 @@
         <v>106</v>
       </c>
       <c r="M10" s="13" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N10" s="13"/>
       <c r="O10" s="13" t="s">
@@ -2697,7 +2711,7 @@
         <v>114</v>
       </c>
       <c r="M11" s="13" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N11" s="13"/>
       <c r="O11" s="13"/>
@@ -2740,7 +2754,7 @@
         <v>114</v>
       </c>
       <c r="M12" s="13" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N12" s="13"/>
       <c r="O12" s="13"/>
@@ -2783,7 +2797,7 @@
         <v>114</v>
       </c>
       <c r="M13" s="13" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N13" s="13"/>
       <c r="O13" s="13"/>
@@ -2826,7 +2840,7 @@
         <v>129</v>
       </c>
       <c r="M14" s="13" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N14" s="13"/>
       <c r="O14" s="13"/>
@@ -2869,7 +2883,7 @@
         <v>129</v>
       </c>
       <c r="M15" s="13" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N15" s="13"/>
       <c r="O15" s="13"/>
@@ -2912,7 +2926,7 @@
         <v>65</v>
       </c>
       <c r="M16" s="13" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N16" s="13"/>
       <c r="O16" s="13"/>
@@ -2954,13 +2968,13 @@
       <c r="L17" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="M17" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="N17" s="13"/>
-      <c r="O17" s="13" t="s">
+      <c r="M17" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="N17" s="13" t="s">
         <v>144</v>
       </c>
+      <c r="O17" s="13"/>
     </row>
     <row r="18" ht="35.049999999999997" customHeight="1">
       <c r="A18" s="13" t="s">
@@ -3000,7 +3014,7 @@
         <v>106</v>
       </c>
       <c r="M18" s="13" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N18" s="13"/>
       <c r="O18" s="13"/>
@@ -3043,7 +3057,7 @@
         <v>106</v>
       </c>
       <c r="M19" s="13" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N19" s="13"/>
       <c r="O19" s="13"/>
@@ -3086,16 +3100,16 @@
         <v>65</v>
       </c>
       <c r="M20" s="13" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N20" s="13"/>
       <c r="O20" s="13" t="s">
-        <v>144</v>
+        <v>161</v>
       </c>
     </row>
     <row r="21" ht="46.25" customHeight="1">
       <c r="A21" s="13" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B21" s="13" t="s">
         <v>17</v>
@@ -3104,7 +3118,7 @@
         <v>58</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E21" s="15" t="s">
         <v>14</v>
@@ -3116,13 +3130,13 @@
         <v>61</v>
       </c>
       <c r="H21" s="13" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I21" s="13" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="J21" s="13" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K21" s="13" t="s">
         <v>55</v>
@@ -3131,16 +3145,16 @@
         <v>65</v>
       </c>
       <c r="M21" s="13" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N21" s="13"/>
       <c r="O21" s="13" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="22" ht="35.049999999999997" customHeight="1">
       <c r="A22" s="13" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B22" s="13" t="s">
         <v>17</v>
@@ -3149,7 +3163,7 @@
         <v>109</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E22" s="15" t="s">
         <v>14</v>
@@ -3161,13 +3175,13 @@
         <v>51</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I22" s="13" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J22" s="13" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K22" s="13" t="s">
         <v>55</v>
@@ -3175,15 +3189,17 @@
       <c r="L22" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="M22" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="N22" s="13"/>
+      <c r="M22" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="N22" s="13" t="s">
+        <v>173</v>
+      </c>
       <c r="O22" s="13"/>
     </row>
     <row r="23" ht="46.25" customHeight="1">
       <c r="A23" s="13" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B23" s="13" t="s">
         <v>17</v>
@@ -3192,7 +3208,7 @@
         <v>58</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E23" s="15" t="s">
         <v>14</v>
@@ -3207,10 +3223,10 @@
         <v>103</v>
       </c>
       <c r="I23" s="13" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="J23" s="13" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="K23" s="13" t="s">
         <v>55</v>
@@ -3219,14 +3235,14 @@
         <v>65</v>
       </c>
       <c r="M23" s="13" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N23" s="13"/>
       <c r="O23" s="13"/>
     </row>
     <row r="24" ht="23.850000000000001" customHeight="1">
       <c r="A24" s="13" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B24" s="13" t="s">
         <v>17</v>
@@ -3235,7 +3251,7 @@
         <v>67</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E24" s="15" t="s">
         <v>14</v>
@@ -3244,16 +3260,16 @@
         <v>75</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H24" s="13" t="s">
         <v>52</v>
       </c>
       <c r="I24" s="13" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="J24" s="13" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K24" s="13" t="s">
         <v>55</v>
@@ -3262,14 +3278,14 @@
         <v>72</v>
       </c>
       <c r="M24" s="13" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N24" s="13"/>
       <c r="O24" s="13"/>
     </row>
     <row r="25" ht="46.25" customHeight="1">
       <c r="A25" s="13" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B25" s="13" t="s">
         <v>17</v>
@@ -3278,7 +3294,7 @@
         <v>67</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E25" s="14" t="s">
         <v>12</v>
@@ -3293,10 +3309,10 @@
         <v>103</v>
       </c>
       <c r="I25" s="13" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="J25" s="13" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="K25" s="13" t="s">
         <v>55</v>
@@ -3305,23 +3321,23 @@
         <v>72</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N25" s="13"/>
       <c r="O25" s="13"/>
     </row>
     <row r="26" ht="23.850000000000001" customHeight="1">
       <c r="A26" s="13" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B26" s="13" t="s">
         <v>17</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E26" s="14" t="s">
         <v>12</v>
@@ -3330,25 +3346,25 @@
         <v>60</v>
       </c>
       <c r="G26" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="H26" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="I26" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="J26" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="K26" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="H26" s="13" t="s">
-        <v>189</v>
-      </c>
-      <c r="I26" s="13" t="s">
-        <v>190</v>
-      </c>
-      <c r="J26" s="13" t="s">
-        <v>191</v>
-      </c>
-      <c r="K26" s="13" t="s">
-        <v>186</v>
-      </c>
       <c r="L26" s="13" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="M26" s="13" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N26" s="13"/>
       <c r="O26" s="13"/>
@@ -3404,18 +3420,1644 @@
           </x14:cfRule>
           <xm:sqref>M2:M26</xm:sqref>
         </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Pass"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC6EFCE"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M18</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Fail"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M18</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Blocked"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFEB9C"/>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M18</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Pass"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC6EFCE"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M19</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Fail"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M19</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Blocked"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFEB9C"/>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M19</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Pass"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC6EFCE"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M19</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Fail"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M19</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Blocked"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFEB9C"/>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M19</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Pass"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC6EFCE"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M20</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Fail"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M20</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Blocked"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFEB9C"/>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M20</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Pass"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC6EFCE"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M20</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Fail"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M20</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Blocked"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFEB9C"/>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M20</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Pass"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC6EFCE"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M20</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Fail"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M20</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Blocked"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFEB9C"/>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M20</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Pass"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC6EFCE"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M21</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Fail"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M21</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Blocked"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFEB9C"/>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M21</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Pass"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC6EFCE"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M21</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Fail"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M21</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Blocked"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFEB9C"/>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M21</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Pass"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC6EFCE"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M21</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Fail"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M21</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Blocked"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFEB9C"/>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M21</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Pass"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC6EFCE"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M21</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Fail"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M21</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Blocked"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFEB9C"/>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M21</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Pass"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC6EFCE"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M22</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Fail"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M22</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Blocked"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFEB9C"/>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M22</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Pass"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC6EFCE"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M23</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Fail"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M23</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Blocked"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFEB9C"/>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M23</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Pass"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC6EFCE"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M23</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Fail"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M23</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Blocked"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFEB9C"/>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M23</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Pass"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC6EFCE"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M23</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Fail"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M23</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Blocked"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFEB9C"/>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M23</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Pass"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC6EFCE"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M23</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Fail"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M23</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Blocked"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFEB9C"/>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M23</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Pass"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC6EFCE"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M23</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Fail"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M23</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Blocked"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFEB9C"/>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M23</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Pass"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC6EFCE"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M24</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Fail"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M24</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Blocked"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFEB9C"/>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M24</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Pass"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC6EFCE"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M24</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Fail"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M24</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Blocked"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFEB9C"/>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M24</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Pass"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC6EFCE"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M24</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Fail"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M24</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Blocked"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFEB9C"/>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M24</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Pass"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC6EFCE"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M24</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Fail"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M24</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Blocked"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFEB9C"/>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M24</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Pass"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC6EFCE"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M24</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Fail"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M24</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Blocked"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFEB9C"/>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M24</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Pass"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC6EFCE"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M24</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Fail"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M24</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Blocked"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFEB9C"/>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M24</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Pass"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC6EFCE"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M25</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Fail"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M25</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Blocked"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFEB9C"/>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M25</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Pass"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC6EFCE"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M25</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Fail"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M25</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Blocked"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFEB9C"/>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M25</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Pass"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC6EFCE"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M25</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Fail"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M25</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Blocked"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFEB9C"/>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M25</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Pass"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC6EFCE"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M25</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Fail"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M25</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Blocked"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFEB9C"/>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M25</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Pass"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC6EFCE"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M25</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Fail"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M25</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Blocked"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFEB9C"/>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M25</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Pass"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC6EFCE"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M25</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Fail"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M25</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Blocked"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFEB9C"/>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M25</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Pass"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC6EFCE"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M25</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Fail"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M25</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Blocked"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFEB9C"/>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M25</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Pass"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC6EFCE"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M26</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Fail"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M26</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Blocked"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFEB9C"/>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M26</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Pass"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC6EFCE"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M26</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Fail"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M26</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Blocked"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFEB9C"/>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M26</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Pass"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC6EFCE"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M26</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Fail"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M26</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Blocked"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFEB9C"/>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M26</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Pass"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC6EFCE"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M26</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Fail"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M26</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Blocked"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFEB9C"/>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M26</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Pass"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC6EFCE"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M26</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Fail"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M26</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Blocked"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFEB9C"/>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M26</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Pass"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC6EFCE"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M26</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Fail"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M26</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Blocked"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFEB9C"/>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M26</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Pass"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC6EFCE"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M26</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Fail"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M26</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Blocked"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFEB9C"/>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M26</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Pass"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC6EFCE"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M26</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Fail"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M26</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Blocked"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFEB9C"/>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M26</xm:sqref>
+        </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1" disablePrompts="0">
-        <x14:dataValidation xr:uid="{7A055AB6-F9B4-4D89-A286-8236C0E60A0A}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="9" disablePrompts="0">
+        <x14:dataValidation xr:uid="{1C1F83F4-DCAD-4900-9F08-46A0ED2A5702}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
           <x14:formula1>
             <xm:f>"Not Run,Pass,Fail,Blocked,Skipped"</xm:f>
           </x14:formula1>
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>M2:M26</xm:sqref>
+          <xm:sqref>M2:M16</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation xr:uid="{29D6183F-1C3D-484B-A87B-EBF39946C35D}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
+          <x14:formula1>
+            <xm:f>"Not Run,Pass,Fail,Blocked,Skipped"</xm:f>
+          </x14:formula1>
+          <x14:formula2>
+            <xm:f>0</xm:f>
+          </x14:formula2>
+          <xm:sqref>M18</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation xr:uid="{701A93A6-75E2-45E9-8984-1EB581FEC577}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
+          <x14:formula1>
+            <xm:f>"Not Run,Pass,Fail,Blocked,Skipped"</xm:f>
+          </x14:formula1>
+          <x14:formula2>
+            <xm:f>0</xm:f>
+          </x14:formula2>
+          <xm:sqref>M19</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation xr:uid="{412503E6-BDBA-4824-ACE6-C26B86AF95DE}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
+          <x14:formula1>
+            <xm:f>"Not Run,Pass,Fail,Blocked,Skipped"</xm:f>
+          </x14:formula1>
+          <x14:formula2>
+            <xm:f>0</xm:f>
+          </x14:formula2>
+          <xm:sqref>M20</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation xr:uid="{3509C0B1-35D4-471B-A8FD-4F06F0E94DB4}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
+          <x14:formula1>
+            <xm:f>"Not Run,Pass,Fail,Blocked,Skipped"</xm:f>
+          </x14:formula1>
+          <x14:formula2>
+            <xm:f>0</xm:f>
+          </x14:formula2>
+          <xm:sqref>M21</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation xr:uid="{54381B46-38F3-4496-A12F-77B4E4F9B3AA}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
+          <x14:formula1>
+            <xm:f>"Not Run,Pass,Fail,Blocked,Skipped"</xm:f>
+          </x14:formula1>
+          <x14:formula2>
+            <xm:f>0</xm:f>
+          </x14:formula2>
+          <xm:sqref>M23</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation xr:uid="{2FF03370-1799-4664-8B94-7F26FF05D694}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
+          <x14:formula1>
+            <xm:f>"Not Run,Pass,Fail,Blocked,Skipped"</xm:f>
+          </x14:formula1>
+          <x14:formula2>
+            <xm:f>0</xm:f>
+          </x14:formula2>
+          <xm:sqref>M24</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation xr:uid="{15F726E3-4587-4069-8DFF-84B80575A152}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
+          <x14:formula1>
+            <xm:f>"Not Run,Pass,Fail,Blocked,Skipped"</xm:f>
+          </x14:formula1>
+          <x14:formula2>
+            <xm:f>0</xm:f>
+          </x14:formula2>
+          <xm:sqref>M25</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation xr:uid="{05AD8129-44E8-4D45-B5BF-17BD74FCB627}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
+          <x14:formula1>
+            <xm:f>"Not Run,Pass,Fail,Blocked,Skipped"</xm:f>
+          </x14:formula1>
+          <x14:formula2>
+            <xm:f>0</xm:f>
+          </x14:formula2>
+          <xm:sqref>M26</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3495,16 +5137,16 @@
     </row>
     <row r="2" ht="46.25" customHeight="1">
       <c r="A2" s="13" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B2" s="13" t="s">
         <v>18</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E2" s="14" t="s">
         <v>12</v>
@@ -3516,19 +5158,19 @@
         <v>51</v>
       </c>
       <c r="H2" s="13" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="I2" s="13" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="J2" s="13" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="K2" s="13" t="s">
         <v>55</v>
       </c>
       <c r="L2" s="13" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="M2" s="13" t="s">
         <v>24</v>
@@ -3538,16 +5180,16 @@
     </row>
     <row r="3" ht="46.25" customHeight="1">
       <c r="A3" s="13" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B3" s="13" t="s">
         <v>18</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E3" s="14" t="s">
         <v>12</v>
@@ -3556,22 +5198,22 @@
         <v>60</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="I3" s="13" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K3" s="13" t="s">
         <v>55</v>
       </c>
       <c r="L3" s="13" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="M3" s="13" t="s">
         <v>24</v>
@@ -3581,16 +5223,16 @@
     </row>
     <row r="4" ht="35.049999999999997" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B4" s="13" t="s">
         <v>18</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E4" s="14" t="s">
         <v>12</v>
@@ -3602,19 +5244,19 @@
         <v>51</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>55</v>
       </c>
       <c r="L4" s="13" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="M4" s="13" t="s">
         <v>24</v>
@@ -3624,16 +5266,16 @@
     </row>
     <row r="5" ht="35.049999999999997" customHeight="1">
       <c r="A5" s="13" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B5" s="13" t="s">
         <v>18</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="E5" s="15" t="s">
         <v>14</v>
@@ -3645,40 +5287,40 @@
         <v>51</v>
       </c>
       <c r="H5" s="13" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="I5" s="13" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="J5" s="13" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="K5" s="13" t="s">
         <v>55</v>
       </c>
       <c r="L5" s="13" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="M5" s="13" t="s">
         <v>24</v>
       </c>
       <c r="N5" s="13"/>
       <c r="O5" s="13" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="6" ht="23.850000000000001" customHeight="1">
       <c r="A6" s="13" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B6" s="13" t="s">
         <v>18</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E6" s="14" t="s">
         <v>12</v>
@@ -3687,22 +5329,22 @@
         <v>60</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H6" s="13" t="s">
         <v>52</v>
       </c>
       <c r="I6" s="13" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="J6" s="13" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="K6" s="13" t="s">
         <v>55</v>
       </c>
       <c r="L6" s="13" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="M6" s="13" t="s">
         <v>24</v>
@@ -3712,16 +5354,16 @@
     </row>
     <row r="7" ht="23.850000000000001" customHeight="1">
       <c r="A7" s="13" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B7" s="13" t="s">
         <v>18</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E7" s="14" t="s">
         <v>12</v>
@@ -3730,22 +5372,22 @@
         <v>50</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H7" s="13" t="s">
         <v>52</v>
       </c>
       <c r="I7" s="13" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="J7" s="13" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="K7" s="13" t="s">
         <v>55</v>
       </c>
       <c r="L7" s="13" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="M7" s="13" t="s">
         <v>24</v>
@@ -3755,16 +5397,16 @@
     </row>
     <row r="8" ht="23.850000000000001" customHeight="1">
       <c r="A8" s="13" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B8" s="13" t="s">
         <v>18</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E8" s="14" t="s">
         <v>12</v>
@@ -3773,22 +5415,22 @@
         <v>50</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="H8" s="13" t="s">
         <v>52</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="K8" s="13" t="s">
         <v>55</v>
       </c>
       <c r="L8" s="13" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="M8" s="13" t="s">
         <v>24</v>
@@ -3798,16 +5440,16 @@
     </row>
     <row r="9" ht="57.450000000000003" customHeight="1">
       <c r="A9" s="13" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B9" s="13" t="s">
         <v>18</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E9" s="14" t="s">
         <v>12</v>
@@ -3816,22 +5458,22 @@
         <v>50</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="K9" s="13" t="s">
         <v>55</v>
       </c>
       <c r="L9" s="13" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="M9" s="13" t="s">
         <v>24</v>
@@ -3841,16 +5483,16 @@
     </row>
     <row r="10" ht="35.049999999999997" customHeight="1">
       <c r="A10" s="13" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B10" s="13" t="s">
         <v>18</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E10" s="14" t="s">
         <v>12</v>
@@ -3859,22 +5501,22 @@
         <v>86</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="H10" s="13" t="s">
         <v>52</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="K10" s="13" t="s">
         <v>55</v>
       </c>
       <c r="L10" s="13" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="M10" s="13" t="s">
         <v>24</v>
@@ -3884,16 +5526,16 @@
     </row>
     <row r="11" ht="35.049999999999997" customHeight="1">
       <c r="A11" s="13" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B11" s="13" t="s">
         <v>18</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E11" s="14" t="s">
         <v>12</v>
@@ -3905,19 +5547,19 @@
         <v>51</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K11" s="13" t="s">
         <v>55</v>
       </c>
       <c r="L11" s="13" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="M11" s="13" t="s">
         <v>24</v>
@@ -3927,16 +5569,16 @@
     </row>
     <row r="12" ht="35.049999999999997" customHeight="1">
       <c r="A12" s="13" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B12" s="13" t="s">
         <v>18</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E12" s="14" t="s">
         <v>12</v>
@@ -3948,19 +5590,19 @@
         <v>51</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="K12" s="13" t="s">
         <v>55</v>
       </c>
       <c r="L12" s="13" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="M12" s="13" t="s">
         <v>24</v>
@@ -3970,16 +5612,16 @@
     </row>
     <row r="13" ht="23.850000000000001" customHeight="1">
       <c r="A13" s="13" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B13" s="13" t="s">
         <v>18</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E13" s="16" t="s">
         <v>13</v>
@@ -3988,22 +5630,22 @@
         <v>50</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="K13" s="13" t="s">
         <v>128</v>
       </c>
       <c r="L13" s="13" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="M13" s="13" t="s">
         <v>24</v>
@@ -4013,16 +5655,16 @@
     </row>
     <row r="14" ht="23.850000000000001" customHeight="1">
       <c r="A14" s="13" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B14" s="13" t="s">
         <v>18</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E14" s="16" t="s">
         <v>13</v>
@@ -4031,22 +5673,22 @@
         <v>60</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="H14" s="13" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="L14" s="13" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="M14" s="13" t="s">
         <v>24</v>
@@ -4056,16 +5698,16 @@
     </row>
     <row r="15" ht="23.850000000000001" customHeight="1">
       <c r="A15" s="13" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B15" s="13" t="s">
         <v>18</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E15" s="16" t="s">
         <v>13</v>
@@ -4074,22 +5716,22 @@
         <v>75</v>
       </c>
       <c r="G15" s="13" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="J15" s="13" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="K15" s="13" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="L15" s="13" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="M15" s="13" t="s">
         <v>24</v>
@@ -4099,16 +5741,16 @@
     </row>
     <row r="16" ht="35.049999999999997" customHeight="1">
       <c r="A16" s="13" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B16" s="13" t="s">
         <v>18</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E16" s="15" t="s">
         <v>14</v>
@@ -4120,40 +5762,40 @@
         <v>51</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="J16" s="13" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="K16" s="13" t="s">
         <v>128</v>
       </c>
       <c r="L16" s="13" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="M16" s="13" t="s">
         <v>24</v>
       </c>
       <c r="N16" s="13"/>
       <c r="O16" s="13" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="17" ht="23.850000000000001" customHeight="1">
       <c r="A17" s="13" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B17" s="13" t="s">
         <v>18</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E17" s="15" t="s">
         <v>14</v>
@@ -4162,22 +5804,22 @@
         <v>75</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="H17" s="13" t="s">
         <v>52</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="J17" s="13" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="K17" s="13" t="s">
         <v>55</v>
       </c>
       <c r="L17" s="13" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="M17" s="13" t="s">
         <v>24</v>
@@ -4187,16 +5829,16 @@
     </row>
     <row r="18" ht="35.049999999999997" customHeight="1">
       <c r="A18" s="13" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B18" s="13" t="s">
         <v>18</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E18" s="15" t="s">
         <v>14</v>
@@ -4208,19 +5850,19 @@
         <v>51</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="J18" s="13" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="K18" s="13" t="s">
         <v>55</v>
       </c>
       <c r="L18" s="13" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="M18" s="13" t="s">
         <v>24</v>
@@ -4230,16 +5872,16 @@
     </row>
     <row r="19" ht="46.25" customHeight="1">
       <c r="A19" s="13" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B19" s="13" t="s">
         <v>18</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="E19" s="14" t="s">
         <v>12</v>
@@ -4248,22 +5890,22 @@
         <v>50</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="J19" s="13" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="K19" s="13" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="L19" s="13" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="M19" s="13" t="s">
         <v>24</v>
@@ -4340,7 +5982,7 @@
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1" disablePrompts="0">
-        <x14:dataValidation xr:uid="{51D5044C-EC53-49BD-8854-157F2F9BE87A}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
+        <x14:dataValidation xr:uid="{49C9940B-44B3-475D-B2CB-BD180AEDD24E}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
           <x14:formula1>
             <xm:f>"Not Run,Pass,Fail,Blocked,Skipped"</xm:f>
           </x14:formula1>
@@ -4424,16 +6066,16 @@
     </row>
     <row r="2" ht="23.850000000000001" customHeight="1">
       <c r="A2" s="13" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B2" s="13" t="s">
         <v>19</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E2" s="14" t="s">
         <v>12</v>
@@ -4442,22 +6084,22 @@
         <v>50</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="H2" s="13" t="s">
         <v>52</v>
       </c>
       <c r="I2" s="13" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="J2" s="13" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="K2" s="13" t="s">
         <v>55</v>
       </c>
       <c r="L2" s="13" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M2" s="13" t="s">
         <v>24</v>
@@ -4467,16 +6109,16 @@
     </row>
     <row r="3" ht="68.650000000000006" customHeight="1">
       <c r="A3" s="13" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B3" s="13" t="s">
         <v>19</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E3" s="14" t="s">
         <v>12</v>
@@ -4485,22 +6127,22 @@
         <v>60</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="I3" s="13" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="K3" s="13" t="s">
         <v>55</v>
       </c>
       <c r="L3" s="13" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M3" s="13" t="s">
         <v>24</v>
@@ -4510,16 +6152,16 @@
     </row>
     <row r="4" ht="35.049999999999997" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B4" s="13" t="s">
         <v>19</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="E4" s="14" t="s">
         <v>12</v>
@@ -4528,22 +6170,22 @@
         <v>50</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>55</v>
       </c>
       <c r="L4" s="13" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M4" s="13" t="s">
         <v>24</v>
@@ -4553,16 +6195,16 @@
     </row>
     <row r="5" ht="35.049999999999997" customHeight="1">
       <c r="A5" s="13" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B5" s="13" t="s">
         <v>19</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E5" s="14" t="s">
         <v>12</v>
@@ -4571,22 +6213,22 @@
         <v>60</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="H5" s="13" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="I5" s="13" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="J5" s="13" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="K5" s="13" t="s">
         <v>55</v>
       </c>
       <c r="L5" s="13" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M5" s="13" t="s">
         <v>24</v>
@@ -4596,16 +6238,16 @@
     </row>
     <row r="6" ht="23.850000000000001" customHeight="1">
       <c r="A6" s="13" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B6" s="13" t="s">
         <v>19</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E6" s="16" t="s">
         <v>13</v>
@@ -4614,22 +6256,22 @@
         <v>50</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="H6" s="13" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="I6" s="13" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="J6" s="13" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="K6" s="13" t="s">
         <v>55</v>
       </c>
       <c r="L6" s="13" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="M6" s="13" t="s">
         <v>24</v>
@@ -4639,16 +6281,16 @@
     </row>
     <row r="7" ht="35.049999999999997" customHeight="1">
       <c r="A7" s="13" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B7" s="13" t="s">
         <v>19</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E7" s="16" t="s">
         <v>13</v>
@@ -4657,22 +6299,22 @@
         <v>50</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="H7" s="13" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="I7" s="13" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="J7" s="13" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="K7" s="13" t="s">
         <v>55</v>
       </c>
       <c r="L7" s="13" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="M7" s="13" t="s">
         <v>24</v>
@@ -4682,16 +6324,16 @@
     </row>
     <row r="8" ht="35.049999999999997" customHeight="1">
       <c r="A8" s="13" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B8" s="13" t="s">
         <v>19</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="E8" s="16" t="s">
         <v>13</v>
@@ -4700,22 +6342,22 @@
         <v>50</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="H8" s="13" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="K8" s="13" t="s">
         <v>55</v>
       </c>
       <c r="L8" s="13" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="M8" s="13" t="s">
         <v>24</v>
@@ -4725,16 +6367,16 @@
     </row>
     <row r="9" ht="46.25" customHeight="1">
       <c r="A9" s="13" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B9" s="13" t="s">
         <v>19</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E9" s="16" t="s">
         <v>13</v>
@@ -4743,22 +6385,22 @@
         <v>75</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="K9" s="13" t="s">
         <v>55</v>
       </c>
       <c r="L9" s="13" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M9" s="13" t="s">
         <v>24</v>
@@ -4768,16 +6410,16 @@
     </row>
     <row r="10" ht="35.049999999999997" customHeight="1">
       <c r="A10" s="13" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B10" s="13" t="s">
         <v>19</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="E10" s="16" t="s">
         <v>13</v>
@@ -4786,43 +6428,43 @@
         <v>50</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="K10" s="13" t="s">
         <v>55</v>
       </c>
       <c r="L10" s="13" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="M10" s="13" t="s">
         <v>24</v>
       </c>
       <c r="N10" s="13"/>
       <c r="O10" s="13" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="11" ht="35.049999999999997" customHeight="1">
       <c r="A11" s="13" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B11" s="13" t="s">
         <v>19</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="E11" s="16" t="s">
         <v>13</v>
@@ -4831,43 +6473,43 @@
         <v>75</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="K11" s="13" t="s">
         <v>55</v>
       </c>
       <c r="L11" s="13" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="M11" s="13" t="s">
         <v>24</v>
       </c>
       <c r="N11" s="13"/>
       <c r="O11" s="13" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="12" ht="35.049999999999997" customHeight="1">
       <c r="A12" s="13" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B12" s="13" t="s">
         <v>19</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="E12" s="16" t="s">
         <v>13</v>
@@ -4876,43 +6518,43 @@
         <v>50</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="K12" s="13" t="s">
         <v>55</v>
       </c>
       <c r="L12" s="13" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="M12" s="13" t="s">
         <v>24</v>
       </c>
       <c r="N12" s="13"/>
       <c r="O12" s="13" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="13" ht="23.850000000000001" customHeight="1">
       <c r="A13" s="13" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B13" s="13" t="s">
         <v>19</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E13" s="15" t="s">
         <v>14</v>
@@ -4921,22 +6563,22 @@
         <v>75</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K13" s="13" t="s">
         <v>55</v>
       </c>
       <c r="L13" s="13" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="M13" s="13" t="s">
         <v>24</v>
@@ -4946,16 +6588,16 @@
     </row>
     <row r="14" ht="23.850000000000001" customHeight="1">
       <c r="A14" s="13" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B14" s="13" t="s">
         <v>19</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="E14" s="15" t="s">
         <v>14</v>
@@ -4964,22 +6606,22 @@
         <v>86</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="H14" s="13" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="K14" s="13" t="s">
         <v>55</v>
       </c>
       <c r="L14" s="13" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="M14" s="13" t="s">
         <v>24</v>
@@ -4989,16 +6631,16 @@
     </row>
     <row r="15" ht="35.049999999999997" customHeight="1">
       <c r="A15" s="13" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B15" s="13" t="s">
         <v>19</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="E15" s="15" t="s">
         <v>14</v>
@@ -5007,22 +6649,22 @@
         <v>86</v>
       </c>
       <c r="G15" s="13" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="J15" s="13" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="K15" s="13" t="s">
         <v>55</v>
       </c>
       <c r="L15" s="13" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M15" s="13" t="s">
         <v>24</v>
@@ -5103,7 +6745,7 @@
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1" disablePrompts="0">
-        <x14:dataValidation xr:uid="{40237662-67AD-4676-8847-52828C683044}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
+        <x14:dataValidation xr:uid="{05693C4F-E1C2-472E-B7C5-440663D94E2D}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
           <x14:formula1>
             <xm:f>"Not Run,Pass,Fail,Blocked,Skipped"</xm:f>
           </x14:formula1>

--- a/00.test_case/Demoblaze_TestCases_Login_Cart.xlsx
+++ b/00.test_case/Demoblaze_TestCases_Login_Cart.xlsx
@@ -4,7 +4,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="1" showHorizontalScroll="1" showVerticalScroll="1"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0" showHorizontalScroll="1" showVerticalScroll="1"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="364">
   <si>
     <t xml:space="preserve">Demoblaze – Test Case Suite (Login, Cart &amp; Order)</t>
   </si>
@@ -108,25 +108,7 @@
     <t xml:space="preserve">Pass rate</t>
   </si>
   <si>
-    <t xml:space="preserve">How to use</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Fill 'Status' (column M, dropdown) and 'Actual Result' (column N) in the Login / Cart / Order sheets during execution.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Counts and pass rate on this sheet update automatically from those columns.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Type colours: green = Functional, orange = Negative, yellow = Edge.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• 'Planned Spec' = Playwright spec that automates the case; the TC ID is the prefix of the test title (e.g. 'LG-002 ...').</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• &lt;TEST_USERNAME&gt;/&lt;TEST_PASSWORD&gt; = account from .env; the framework creates one automatically if not set.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Notes 'Confirm with BA' mark expected results where the business rule is not documented by the app.</t>
+    <t xml:space="preserve">Execution rate</t>
   </si>
   <si>
     <t xml:space="preserve">TC ID</t>
@@ -1382,7 +1364,7 @@
     <xf fontId="1" fillId="0" borderId="0" numFmtId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" quotePrefix="0" pivotButton="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" quotePrefix="0" pivotButton="0"/>
     <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" quotePrefix="0" pivotButton="0"/>
@@ -1402,6 +1384,10 @@
     <xf fontId="5" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" quotePrefix="0" pivotButton="0"/>
     <xf fontId="1" fillId="0" borderId="1" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="9" xfId="0" applyNumberFormat="1" quotePrefix="0" pivotButton="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" quotePrefix="0" pivotButton="0">
+      <protection hidden="0" locked="1"/>
     </xf>
     <xf fontId="4" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1901,6 +1887,7 @@
   <cols>
     <col customWidth="1" min="1" max="1" style="1" width="26"/>
     <col customWidth="1" min="2" max="6" style="1" width="14"/>
+    <col customWidth="1" min="7" max="7" width="14.421875"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.350000000000001" customHeight="1">
@@ -2092,6 +2079,9 @@
       <c r="F17" s="5" t="s">
         <v>25</v>
       </c>
+      <c r="G17" s="5" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" s="6" t="s">
@@ -2117,6 +2107,10 @@
         <f t="shared" ref="F18:F20" si="1">IFERROR(B18/(B18+C18+D18),0)</f>
         <v>0.92</v>
       </c>
+      <c r="G18" s="12">
+        <f>1-E18/E11</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" s="6" t="s">
@@ -2142,6 +2136,10 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
+      <c r="G19" s="12">
+        <f>1-E19/E12</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" s="6" t="s">
@@ -2167,42 +2165,83 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
+      <c r="G20" s="12">
+        <f>1-E20/E13</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="21" ht="15" customHeight="1"/>
     <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="10" t="s">
-        <v>26</v>
-      </c>
+      <c r="A22" s="13"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13"/>
     </row>
     <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="4" t="s">
-        <v>27</v>
-      </c>
+      <c r="A23" s="13"/>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="13"/>
     </row>
     <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="4" t="s">
-        <v>28</v>
-      </c>
+      <c r="A24" s="13"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="13"/>
     </row>
     <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="4" t="s">
-        <v>29</v>
-      </c>
+      <c r="A25" s="13"/>
+      <c r="B25" s="13"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="13"/>
     </row>
     <row r="26" ht="15" customHeight="1">
-      <c r="A26" s="4" t="s">
-        <v>30</v>
-      </c>
+      <c r="A26" s="13"/>
+      <c r="B26" s="13"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="13"/>
     </row>
     <row r="27" ht="15" customHeight="1">
-      <c r="A27" s="4" t="s">
-        <v>31</v>
-      </c>
+      <c r="A27" s="13"/>
+      <c r="B27" s="13"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="13"/>
+      <c r="G27" s="13"/>
     </row>
     <row r="28" ht="15" customHeight="1">
-      <c r="A28" s="4" t="s">
-        <v>32</v>
-      </c>
+      <c r="A28" s="13"/>
+      <c r="B28" s="13"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="13"/>
+    </row>
+    <row r="29" ht="14.25">
+      <c r="A29" s="13"/>
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="13"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0" horizontalCentered="0" verticalCentered="0"/>
@@ -2236,1138 +2275,1138 @@
   </cols>
   <sheetData>
     <row r="1" ht="23.850000000000001" customHeight="1">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="H1" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C1" s="12" t="s">
+      <c r="I1" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="J1" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="K1" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="L1" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="M1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="N1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="O1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="J1" s="12" t="s">
+    </row>
+    <row r="2" ht="35.049999999999997" customHeight="1">
+      <c r="A2" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="B2" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="L1" s="12" t="s">
+      <c r="D2" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="M1" s="12" t="s">
+      <c r="E2" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="N1" s="12" t="s">
+      <c r="G2" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="O1" s="12" t="s">
+      <c r="H2" s="15" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="2" ht="35.049999999999997" customHeight="1">
-      <c r="A2" s="13" t="s">
+      <c r="I2" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="J2" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="K2" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L2" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="M2" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="N2" s="15"/>
+      <c r="O2" s="15"/>
+    </row>
+    <row r="3" ht="46.25" customHeight="1">
+      <c r="A3" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="D2" s="13" t="s">
+      <c r="C3" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="H3" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="I3" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="J3" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="K3" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="L3" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="M3" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="N3" s="15"/>
+      <c r="O3" s="15"/>
+    </row>
+    <row r="4" ht="23.850000000000001" customHeight="1">
+      <c r="A4" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="E4" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="F4" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="G4" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="H4" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="I4" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="J4" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="K4" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L4" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="M4" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="N4" s="15"/>
+      <c r="O4" s="15"/>
+    </row>
+    <row r="5" ht="46.25" customHeight="1">
+      <c r="A5" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="G5" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="H5" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="I5" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="J5" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="K5" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L5" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="M5" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="N5" s="15"/>
+      <c r="O5" s="15"/>
+    </row>
+    <row r="6" ht="35.049999999999997" customHeight="1">
+      <c r="A6" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G6" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="H6" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="I6" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="J6" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="K6" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L6" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="M6" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="N6" s="15"/>
+      <c r="O6" s="15"/>
+    </row>
+    <row r="7" ht="35.049999999999997" customHeight="1">
+      <c r="A7" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="G7" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="H7" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="I7" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="J7" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="K7" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L7" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="G2" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="H2" s="13" t="s">
+      <c r="M7" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="N7" s="15"/>
+      <c r="O7" s="15"/>
+    </row>
+    <row r="8" ht="35.049999999999997" customHeight="1">
+      <c r="A8" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="G8" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="H8" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="I8" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="J8" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="K8" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L8" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="M8" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="N8" s="15"/>
+      <c r="O8" s="15"/>
+    </row>
+    <row r="9" ht="35.049999999999997" customHeight="1">
+      <c r="A9" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="I2" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="J2" s="13" t="s">
+      <c r="D9" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="G9" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="H9" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="I9" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="J9" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="K9" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L9" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="M9" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="N9" s="15"/>
+      <c r="O9" s="15" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="10" ht="46.25" customHeight="1">
+      <c r="A10" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="G10" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="H10" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="I10" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="J10" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="K10" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L10" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="M10" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="N10" s="15"/>
+      <c r="O10" s="15" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="11" ht="35.049999999999997" customHeight="1">
+      <c r="A11" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="E11" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="G11" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="H11" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="I11" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="J11" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="K11" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L11" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="M11" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="N11" s="15"/>
+      <c r="O11" s="15"/>
+    </row>
+    <row r="12" ht="35.049999999999997" customHeight="1">
+      <c r="A12" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="E12" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="G12" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="H12" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="I12" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="J12" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="K12" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L12" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="M12" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="N12" s="15"/>
+      <c r="O12" s="15"/>
+    </row>
+    <row r="13" ht="35.049999999999997" customHeight="1">
+      <c r="A13" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="E13" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="G13" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="H13" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="I13" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="J13" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="K13" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L13" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="M13" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="N13" s="15"/>
+      <c r="O13" s="15"/>
+    </row>
+    <row r="14" ht="46.25" customHeight="1">
+      <c r="A14" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="K2" s="13" t="s">
+      <c r="G14" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="L2" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="M2" s="13" t="s">
+      <c r="H14" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="I14" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="J14" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="K14" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="L14" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="M14" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="N2" s="13"/>
-      <c r="O2" s="13"/>
-    </row>
-    <row r="3" ht="46.25" customHeight="1">
-      <c r="A3" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="B3" s="13" t="s">
+      <c r="N14" s="15"/>
+      <c r="O14" s="15"/>
+    </row>
+    <row r="15" ht="35.049999999999997" customHeight="1">
+      <c r="A15" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="B15" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="D3" s="13" t="s">
+      <c r="C15" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="E15" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G15" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="H15" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="I15" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="J15" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="K15" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="L15" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="M15" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="N15" s="15"/>
+      <c r="O15" s="15"/>
+    </row>
+    <row r="16" ht="46.25" customHeight="1">
+      <c r="A16" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="E16" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="G16" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="H16" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="I16" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="J16" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="K16" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L16" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="M16" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="N16" s="15"/>
+      <c r="O16" s="15"/>
+    </row>
+    <row r="17" ht="35.049999999999997" customHeight="1">
+      <c r="A17" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="E17" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F17" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="G17" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="H17" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="I17" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="J17" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="K17" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L17" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="M17" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="N17" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="O17" s="15"/>
+    </row>
+    <row r="18" ht="35.049999999999997" customHeight="1">
+      <c r="A18" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="E18" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="G18" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="H18" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="I18" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="J18" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="K18" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L18" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="M18" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="N18" s="15"/>
+      <c r="O18" s="15"/>
+    </row>
+    <row r="19" ht="35.049999999999997" customHeight="1">
+      <c r="A19" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="E19" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="G19" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="H19" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="I19" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="J19" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="K19" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L19" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="M19" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="N19" s="15"/>
+      <c r="O19" s="15"/>
+    </row>
+    <row r="20" ht="46.25" customHeight="1">
+      <c r="A20" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="D20" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="F20" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="G20" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="H20" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="I20" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="J20" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="K20" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L20" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="M20" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="N20" s="15"/>
+      <c r="O20" s="15" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="21" ht="46.25" customHeight="1">
+      <c r="A21" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="E21" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="F21" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="G21" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="H21" s="15" t="s">
+        <v>158</v>
+      </c>
+      <c r="I21" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="J21" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="K21" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L21" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="M21" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="N21" s="15"/>
+      <c r="O21" s="15" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="22" ht="35.049999999999997" customHeight="1">
+      <c r="A22" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="B22" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="D22" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="E22" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="F22" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="G22" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="H22" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="I22" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="J22" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="K22" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L22" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="M22" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="N22" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="O22" s="15"/>
+    </row>
+    <row r="23" ht="46.25" customHeight="1">
+      <c r="A23" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="B23" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="D23" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="E23" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="F23" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="G23" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="H23" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="I23" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="J23" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="K23" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L23" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="M23" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="N23" s="15"/>
+      <c r="O23" s="15"/>
+    </row>
+    <row r="24" ht="23.850000000000001" customHeight="1">
+      <c r="A24" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="B24" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C24" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="D24" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="E24" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="F24" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="G24" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="H24" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="I24" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="J24" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="K24" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L24" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="M24" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="N24" s="15"/>
+      <c r="O24" s="15"/>
+    </row>
+    <row r="25" ht="46.25" customHeight="1">
+      <c r="A25" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="B25" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="D25" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="E25" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="G3" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="H3" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="I3" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="J3" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="K3" s="13" t="s">
+      <c r="F25" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="G25" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="L3" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="M3" s="13" t="s">
+      <c r="H25" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="I25" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="J25" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="K25" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L25" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="M25" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="N3" s="13"/>
-      <c r="O3" s="13"/>
-    </row>
-    <row r="4" ht="23.850000000000001" customHeight="1">
-      <c r="A4" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="B4" s="13" t="s">
+      <c r="N25" s="15"/>
+      <c r="O25" s="15"/>
+    </row>
+    <row r="26" ht="23.850000000000001" customHeight="1">
+      <c r="A26" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="B26" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="E4" s="14" t="s">
+      <c r="C26" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="D26" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="E26" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="G4" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="H4" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="I4" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="J4" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="K4" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="L4" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="M4" s="13" t="s">
+      <c r="F26" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G26" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="H26" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="I26" s="15" t="s">
+        <v>186</v>
+      </c>
+      <c r="J26" s="15" t="s">
+        <v>187</v>
+      </c>
+      <c r="K26" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="L26" s="15" t="s">
+        <v>188</v>
+      </c>
+      <c r="M26" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="N4" s="13"/>
-      <c r="O4" s="13"/>
-    </row>
-    <row r="5" ht="46.25" customHeight="1">
-      <c r="A5" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G5" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="H5" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="I5" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="J5" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="K5" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="L5" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="M5" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="N5" s="13"/>
-      <c r="O5" s="13"/>
-    </row>
-    <row r="6" ht="35.049999999999997" customHeight="1">
-      <c r="A6" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="G6" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="H6" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="I6" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="J6" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="K6" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="L6" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="M6" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="N6" s="13"/>
-      <c r="O6" s="13"/>
-    </row>
-    <row r="7" ht="35.049999999999997" customHeight="1">
-      <c r="A7" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="G7" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="H7" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="I7" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="J7" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="K7" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="L7" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="M7" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="N7" s="13"/>
-      <c r="O7" s="13"/>
-    </row>
-    <row r="8" ht="35.049999999999997" customHeight="1">
-      <c r="A8" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G8" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="H8" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="I8" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="J8" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="K8" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="L8" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="M8" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="N8" s="13"/>
-      <c r="O8" s="13"/>
-    </row>
-    <row r="9" ht="35.049999999999997" customHeight="1">
-      <c r="A9" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="E9" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="F9" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G9" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="H9" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="I9" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="J9" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="K9" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="L9" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="M9" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="N9" s="13"/>
-      <c r="O9" s="13" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10" ht="46.25" customHeight="1">
-      <c r="A10" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="E10" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G10" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="H10" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="I10" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="J10" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="K10" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="L10" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="M10" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="N10" s="13"/>
-      <c r="O10" s="13" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="11" ht="35.049999999999997" customHeight="1">
-      <c r="A11" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="E11" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="G11" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="H11" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="I11" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="J11" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="K11" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="L11" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="M11" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="N11" s="13"/>
-      <c r="O11" s="13"/>
-    </row>
-    <row r="12" ht="35.049999999999997" customHeight="1">
-      <c r="A12" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>116</v>
-      </c>
-      <c r="E12" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="G12" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="H12" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="I12" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="J12" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="K12" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="L12" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="M12" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="N12" s="13"/>
-      <c r="O12" s="13"/>
-    </row>
-    <row r="13" ht="35.049999999999997" customHeight="1">
-      <c r="A13" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="D13" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="E13" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="F13" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="G13" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="H13" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="I13" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="J13" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="K13" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="L13" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="M13" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="N13" s="13"/>
-      <c r="O13" s="13"/>
-    </row>
-    <row r="14" ht="46.25" customHeight="1">
-      <c r="A14" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="B14" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>124</v>
-      </c>
-      <c r="E14" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="G14" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="I14" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="J14" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="K14" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="L14" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="M14" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="N14" s="13"/>
-      <c r="O14" s="13"/>
-    </row>
-    <row r="15" ht="35.049999999999997" customHeight="1">
-      <c r="A15" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="E15" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="G15" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="I15" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="J15" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="K15" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="L15" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="M15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="N15" s="13"/>
-      <c r="O15" s="13"/>
-    </row>
-    <row r="16" ht="46.25" customHeight="1">
-      <c r="A16" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="B16" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="E16" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="F16" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="G16" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="H16" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="I16" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="J16" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="K16" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="L16" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="M16" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="N16" s="13"/>
-      <c r="O16" s="13"/>
-    </row>
-    <row r="17" ht="35.049999999999997" customHeight="1">
-      <c r="A17" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="B17" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="E17" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="F17" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G17" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="H17" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="I17" s="13" t="s">
-        <v>142</v>
-      </c>
-      <c r="J17" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="K17" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="L17" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="M17" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="N17" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="O17" s="13"/>
-    </row>
-    <row r="18" ht="35.049999999999997" customHeight="1">
-      <c r="A18" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="B18" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C18" s="13" t="s">
-        <v>146</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="E18" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="F18" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="G18" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="H18" s="13" t="s">
-        <v>148</v>
-      </c>
-      <c r="I18" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="J18" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="K18" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="L18" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="M18" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="N18" s="13"/>
-      <c r="O18" s="13"/>
-    </row>
-    <row r="19" ht="35.049999999999997" customHeight="1">
-      <c r="A19" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="B19" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C19" s="13" t="s">
-        <v>146</v>
-      </c>
-      <c r="D19" s="13" t="s">
-        <v>152</v>
-      </c>
-      <c r="E19" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="F19" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="G19" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="H19" s="13" t="s">
-        <v>153</v>
-      </c>
-      <c r="I19" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="J19" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="K19" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="L19" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="M19" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="N19" s="13"/>
-      <c r="O19" s="13"/>
-    </row>
-    <row r="20" ht="46.25" customHeight="1">
-      <c r="A20" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="B20" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C20" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>157</v>
-      </c>
-      <c r="E20" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="F20" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G20" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="H20" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="I20" s="13" t="s">
-        <v>159</v>
-      </c>
-      <c r="J20" s="13" t="s">
-        <v>160</v>
-      </c>
-      <c r="K20" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="L20" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="M20" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="N20" s="13"/>
-      <c r="O20" s="13" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="21" ht="46.25" customHeight="1">
-      <c r="A21" s="13" t="s">
-        <v>162</v>
-      </c>
-      <c r="B21" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C21" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="D21" s="13" t="s">
-        <v>163</v>
-      </c>
-      <c r="E21" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="F21" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G21" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="H21" s="13" t="s">
-        <v>164</v>
-      </c>
-      <c r="I21" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="J21" s="13" t="s">
-        <v>166</v>
-      </c>
-      <c r="K21" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="L21" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="M21" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="N21" s="13"/>
-      <c r="O21" s="13" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="22" ht="35.049999999999997" customHeight="1">
-      <c r="A22" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="B22" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C22" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>169</v>
-      </c>
-      <c r="E22" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="G22" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>170</v>
-      </c>
-      <c r="I22" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="J22" s="13" t="s">
-        <v>172</v>
-      </c>
-      <c r="K22" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="L22" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="M22" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="N22" s="13" t="s">
-        <v>173</v>
-      </c>
-      <c r="O22" s="13"/>
-    </row>
-    <row r="23" ht="46.25" customHeight="1">
-      <c r="A23" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="B23" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C23" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>175</v>
-      </c>
-      <c r="E23" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="F23" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="G23" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="H23" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="I23" s="13" t="s">
-        <v>176</v>
-      </c>
-      <c r="J23" s="13" t="s">
-        <v>177</v>
-      </c>
-      <c r="K23" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="L23" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="M23" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="N23" s="13"/>
-      <c r="O23" s="13"/>
-    </row>
-    <row r="24" ht="23.850000000000001" customHeight="1">
-      <c r="A24" s="13" t="s">
-        <v>178</v>
-      </c>
-      <c r="B24" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C24" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="D24" s="13" t="s">
-        <v>179</v>
-      </c>
-      <c r="E24" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="F24" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G24" s="13" t="s">
-        <v>180</v>
-      </c>
-      <c r="H24" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="I24" s="13" t="s">
-        <v>181</v>
-      </c>
-      <c r="J24" s="13" t="s">
-        <v>182</v>
-      </c>
-      <c r="K24" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="L24" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="M24" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="N24" s="13"/>
-      <c r="O24" s="13"/>
-    </row>
-    <row r="25" ht="46.25" customHeight="1">
-      <c r="A25" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="B25" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C25" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="D25" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="E25" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="F25" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G25" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="H25" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="I25" s="13" t="s">
-        <v>185</v>
-      </c>
-      <c r="J25" s="13" t="s">
-        <v>186</v>
-      </c>
-      <c r="K25" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="L25" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="M25" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="N25" s="13"/>
-      <c r="O25" s="13"/>
-    </row>
-    <row r="26" ht="23.850000000000001" customHeight="1">
-      <c r="A26" s="13" t="s">
-        <v>187</v>
-      </c>
-      <c r="B26" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C26" s="13" t="s">
-        <v>188</v>
-      </c>
-      <c r="D26" s="13" t="s">
-        <v>189</v>
-      </c>
-      <c r="E26" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="F26" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="G26" s="13" t="s">
-        <v>190</v>
-      </c>
-      <c r="H26" s="13" t="s">
-        <v>191</v>
-      </c>
-      <c r="I26" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="J26" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="K26" s="13" t="s">
-        <v>188</v>
-      </c>
-      <c r="L26" s="13" t="s">
-        <v>194</v>
-      </c>
-      <c r="M26" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="N26" s="13"/>
-      <c r="O26" s="13"/>
+      <c r="N26" s="15"/>
+      <c r="O26" s="15"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:O26"/>
@@ -3421,7 +3460,7 @@
           <xm:sqref>M2:M26</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="5" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Pass"</xm:f>
             <x14:dxf>
               <fill>
@@ -3435,7 +3474,7 @@
           <xm:sqref>M18</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="6" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Fail"</xm:f>
             <x14:dxf>
               <fill>
@@ -3449,7 +3488,7 @@
           <xm:sqref>M18</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="7" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Blocked"</xm:f>
             <x14:dxf>
               <fill>
@@ -3463,7 +3502,7 @@
           <xm:sqref>M18</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="8" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Pass"</xm:f>
             <x14:dxf>
               <fill>
@@ -3477,7 +3516,7 @@
           <xm:sqref>M19</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="9" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Fail"</xm:f>
             <x14:dxf>
               <fill>
@@ -3491,7 +3530,7 @@
           <xm:sqref>M19</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="10" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Blocked"</xm:f>
             <x14:dxf>
               <fill>
@@ -3505,7 +3544,7 @@
           <xm:sqref>M19</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="11" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Pass"</xm:f>
             <x14:dxf>
               <fill>
@@ -3519,7 +3558,7 @@
           <xm:sqref>M19</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="12" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Fail"</xm:f>
             <x14:dxf>
               <fill>
@@ -3533,7 +3572,7 @@
           <xm:sqref>M19</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="13" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Blocked"</xm:f>
             <x14:dxf>
               <fill>
@@ -3547,7 +3586,7 @@
           <xm:sqref>M19</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="14" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Pass"</xm:f>
             <x14:dxf>
               <fill>
@@ -3561,7 +3600,7 @@
           <xm:sqref>M20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="15" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Fail"</xm:f>
             <x14:dxf>
               <fill>
@@ -3575,7 +3614,7 @@
           <xm:sqref>M20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="16" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Blocked"</xm:f>
             <x14:dxf>
               <fill>
@@ -3589,7 +3628,7 @@
           <xm:sqref>M20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="17" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Pass"</xm:f>
             <x14:dxf>
               <fill>
@@ -3603,7 +3642,7 @@
           <xm:sqref>M20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="18" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Fail"</xm:f>
             <x14:dxf>
               <fill>
@@ -3617,7 +3656,7 @@
           <xm:sqref>M20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="19" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Blocked"</xm:f>
             <x14:dxf>
               <fill>
@@ -3631,7 +3670,7 @@
           <xm:sqref>M20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="20" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Pass"</xm:f>
             <x14:dxf>
               <fill>
@@ -3645,7 +3684,7 @@
           <xm:sqref>M20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="21" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Fail"</xm:f>
             <x14:dxf>
               <fill>
@@ -3659,7 +3698,7 @@
           <xm:sqref>M20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="22" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Blocked"</xm:f>
             <x14:dxf>
               <fill>
@@ -3673,7 +3712,7 @@
           <xm:sqref>M20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="23" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Pass"</xm:f>
             <x14:dxf>
               <fill>
@@ -3687,7 +3726,7 @@
           <xm:sqref>M21</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="24" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Fail"</xm:f>
             <x14:dxf>
               <fill>
@@ -3701,7 +3740,7 @@
           <xm:sqref>M21</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="25" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Blocked"</xm:f>
             <x14:dxf>
               <fill>
@@ -3715,7 +3754,7 @@
           <xm:sqref>M21</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="26" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Pass"</xm:f>
             <x14:dxf>
               <fill>
@@ -3729,7 +3768,7 @@
           <xm:sqref>M21</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="27" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Fail"</xm:f>
             <x14:dxf>
               <fill>
@@ -3743,7 +3782,7 @@
           <xm:sqref>M21</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="28" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Blocked"</xm:f>
             <x14:dxf>
               <fill>
@@ -3757,7 +3796,7 @@
           <xm:sqref>M21</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="29" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Pass"</xm:f>
             <x14:dxf>
               <fill>
@@ -3771,7 +3810,7 @@
           <xm:sqref>M21</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="30" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Fail"</xm:f>
             <x14:dxf>
               <fill>
@@ -3785,7 +3824,7 @@
           <xm:sqref>M21</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="31" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Blocked"</xm:f>
             <x14:dxf>
               <fill>
@@ -3799,7 +3838,7 @@
           <xm:sqref>M21</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="32" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Pass"</xm:f>
             <x14:dxf>
               <fill>
@@ -3813,7 +3852,7 @@
           <xm:sqref>M21</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="33" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Fail"</xm:f>
             <x14:dxf>
               <fill>
@@ -3827,7 +3866,7 @@
           <xm:sqref>M21</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="34" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Blocked"</xm:f>
             <x14:dxf>
               <fill>
@@ -3841,7 +3880,7 @@
           <xm:sqref>M21</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="35" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Pass"</xm:f>
             <x14:dxf>
               <fill>
@@ -3855,7 +3894,7 @@
           <xm:sqref>M22</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="36" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Fail"</xm:f>
             <x14:dxf>
               <fill>
@@ -3869,7 +3908,7 @@
           <xm:sqref>M22</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="37" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Blocked"</xm:f>
             <x14:dxf>
               <fill>
@@ -3883,7 +3922,7 @@
           <xm:sqref>M22</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="38" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Pass"</xm:f>
             <x14:dxf>
               <fill>
@@ -3897,7 +3936,7 @@
           <xm:sqref>M23</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="39" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Fail"</xm:f>
             <x14:dxf>
               <fill>
@@ -3911,7 +3950,7 @@
           <xm:sqref>M23</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="40" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Blocked"</xm:f>
             <x14:dxf>
               <fill>
@@ -3925,7 +3964,7 @@
           <xm:sqref>M23</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="41" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Pass"</xm:f>
             <x14:dxf>
               <fill>
@@ -3939,7 +3978,7 @@
           <xm:sqref>M23</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="42" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Fail"</xm:f>
             <x14:dxf>
               <fill>
@@ -3953,7 +3992,7 @@
           <xm:sqref>M23</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="43" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Blocked"</xm:f>
             <x14:dxf>
               <fill>
@@ -3967,7 +4006,7 @@
           <xm:sqref>M23</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="44" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Pass"</xm:f>
             <x14:dxf>
               <fill>
@@ -3981,7 +4020,7 @@
           <xm:sqref>M23</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="45" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Fail"</xm:f>
             <x14:dxf>
               <fill>
@@ -3995,7 +4034,7 @@
           <xm:sqref>M23</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="46" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Blocked"</xm:f>
             <x14:dxf>
               <fill>
@@ -4009,7 +4048,7 @@
           <xm:sqref>M23</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="47" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Pass"</xm:f>
             <x14:dxf>
               <fill>
@@ -4023,7 +4062,7 @@
           <xm:sqref>M23</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="48" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Fail"</xm:f>
             <x14:dxf>
               <fill>
@@ -4037,7 +4076,7 @@
           <xm:sqref>M23</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="49" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Blocked"</xm:f>
             <x14:dxf>
               <fill>
@@ -4051,7 +4090,7 @@
           <xm:sqref>M23</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="50" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Pass"</xm:f>
             <x14:dxf>
               <fill>
@@ -4065,7 +4104,7 @@
           <xm:sqref>M23</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="51" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Fail"</xm:f>
             <x14:dxf>
               <fill>
@@ -4079,7 +4118,7 @@
           <xm:sqref>M23</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="52" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Blocked"</xm:f>
             <x14:dxf>
               <fill>
@@ -4093,7 +4132,7 @@
           <xm:sqref>M23</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="53" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Pass"</xm:f>
             <x14:dxf>
               <fill>
@@ -4107,7 +4146,7 @@
           <xm:sqref>M24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="54" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Fail"</xm:f>
             <x14:dxf>
               <fill>
@@ -4121,7 +4160,7 @@
           <xm:sqref>M24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="55" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Blocked"</xm:f>
             <x14:dxf>
               <fill>
@@ -4135,7 +4174,7 @@
           <xm:sqref>M24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="56" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Pass"</xm:f>
             <x14:dxf>
               <fill>
@@ -4149,7 +4188,7 @@
           <xm:sqref>M24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="57" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Fail"</xm:f>
             <x14:dxf>
               <fill>
@@ -4163,7 +4202,7 @@
           <xm:sqref>M24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="58" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Blocked"</xm:f>
             <x14:dxf>
               <fill>
@@ -4177,7 +4216,7 @@
           <xm:sqref>M24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="59" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Pass"</xm:f>
             <x14:dxf>
               <fill>
@@ -4191,7 +4230,7 @@
           <xm:sqref>M24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="60" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Fail"</xm:f>
             <x14:dxf>
               <fill>
@@ -4205,7 +4244,7 @@
           <xm:sqref>M24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="61" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Blocked"</xm:f>
             <x14:dxf>
               <fill>
@@ -4219,7 +4258,7 @@
           <xm:sqref>M24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="62" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Pass"</xm:f>
             <x14:dxf>
               <fill>
@@ -4233,7 +4272,7 @@
           <xm:sqref>M24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="63" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Fail"</xm:f>
             <x14:dxf>
               <fill>
@@ -4247,7 +4286,7 @@
           <xm:sqref>M24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="64" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Blocked"</xm:f>
             <x14:dxf>
               <fill>
@@ -4261,7 +4300,7 @@
           <xm:sqref>M24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="65" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Pass"</xm:f>
             <x14:dxf>
               <fill>
@@ -4275,7 +4314,7 @@
           <xm:sqref>M24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="66" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Fail"</xm:f>
             <x14:dxf>
               <fill>
@@ -4289,7 +4328,7 @@
           <xm:sqref>M24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="67" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Blocked"</xm:f>
             <x14:dxf>
               <fill>
@@ -4303,7 +4342,7 @@
           <xm:sqref>M24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="68" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Pass"</xm:f>
             <x14:dxf>
               <fill>
@@ -4317,7 +4356,7 @@
           <xm:sqref>M24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="69" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Fail"</xm:f>
             <x14:dxf>
               <fill>
@@ -4331,7 +4370,7 @@
           <xm:sqref>M24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="70" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Blocked"</xm:f>
             <x14:dxf>
               <fill>
@@ -4345,7 +4384,7 @@
           <xm:sqref>M24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="71" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Pass"</xm:f>
             <x14:dxf>
               <fill>
@@ -4359,7 +4398,7 @@
           <xm:sqref>M25</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="72" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Fail"</xm:f>
             <x14:dxf>
               <fill>
@@ -4373,7 +4412,7 @@
           <xm:sqref>M25</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="73" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Blocked"</xm:f>
             <x14:dxf>
               <fill>
@@ -4387,7 +4426,7 @@
           <xm:sqref>M25</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="74" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Pass"</xm:f>
             <x14:dxf>
               <fill>
@@ -4401,7 +4440,7 @@
           <xm:sqref>M25</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="75" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Fail"</xm:f>
             <x14:dxf>
               <fill>
@@ -4415,7 +4454,7 @@
           <xm:sqref>M25</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="76" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Blocked"</xm:f>
             <x14:dxf>
               <fill>
@@ -4429,7 +4468,7 @@
           <xm:sqref>M25</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="77" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Pass"</xm:f>
             <x14:dxf>
               <fill>
@@ -4443,7 +4482,7 @@
           <xm:sqref>M25</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="78" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Fail"</xm:f>
             <x14:dxf>
               <fill>
@@ -4457,7 +4496,7 @@
           <xm:sqref>M25</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="79" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Blocked"</xm:f>
             <x14:dxf>
               <fill>
@@ -4471,7 +4510,7 @@
           <xm:sqref>M25</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="80" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Pass"</xm:f>
             <x14:dxf>
               <fill>
@@ -4485,7 +4524,7 @@
           <xm:sqref>M25</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="81" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Fail"</xm:f>
             <x14:dxf>
               <fill>
@@ -4499,7 +4538,7 @@
           <xm:sqref>M25</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="82" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Blocked"</xm:f>
             <x14:dxf>
               <fill>
@@ -4513,7 +4552,7 @@
           <xm:sqref>M25</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="83" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Pass"</xm:f>
             <x14:dxf>
               <fill>
@@ -4527,7 +4566,7 @@
           <xm:sqref>M25</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="84" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Fail"</xm:f>
             <x14:dxf>
               <fill>
@@ -4541,7 +4580,7 @@
           <xm:sqref>M25</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="85" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Blocked"</xm:f>
             <x14:dxf>
               <fill>
@@ -4555,7 +4594,7 @@
           <xm:sqref>M25</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="86" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Pass"</xm:f>
             <x14:dxf>
               <fill>
@@ -4569,7 +4608,7 @@
           <xm:sqref>M25</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="87" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Fail"</xm:f>
             <x14:dxf>
               <fill>
@@ -4583,7 +4622,7 @@
           <xm:sqref>M25</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="88" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Blocked"</xm:f>
             <x14:dxf>
               <fill>
@@ -4597,7 +4636,7 @@
           <xm:sqref>M25</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="89" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Pass"</xm:f>
             <x14:dxf>
               <fill>
@@ -4611,7 +4650,7 @@
           <xm:sqref>M25</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="90" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Fail"</xm:f>
             <x14:dxf>
               <fill>
@@ -4625,7 +4664,7 @@
           <xm:sqref>M25</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="91" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Blocked"</xm:f>
             <x14:dxf>
               <fill>
@@ -4639,7 +4678,7 @@
           <xm:sqref>M25</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="92" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Pass"</xm:f>
             <x14:dxf>
               <fill>
@@ -4653,7 +4692,7 @@
           <xm:sqref>M26</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="93" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Fail"</xm:f>
             <x14:dxf>
               <fill>
@@ -4667,7 +4706,7 @@
           <xm:sqref>M26</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="94" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Blocked"</xm:f>
             <x14:dxf>
               <fill>
@@ -4681,7 +4720,7 @@
           <xm:sqref>M26</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="95" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Pass"</xm:f>
             <x14:dxf>
               <fill>
@@ -4695,7 +4734,7 @@
           <xm:sqref>M26</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="96" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Fail"</xm:f>
             <x14:dxf>
               <fill>
@@ -4709,7 +4748,7 @@
           <xm:sqref>M26</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="97" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Blocked"</xm:f>
             <x14:dxf>
               <fill>
@@ -4723,7 +4762,7 @@
           <xm:sqref>M26</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="98" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Pass"</xm:f>
             <x14:dxf>
               <fill>
@@ -4737,7 +4776,7 @@
           <xm:sqref>M26</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="99" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Fail"</xm:f>
             <x14:dxf>
               <fill>
@@ -4751,7 +4790,7 @@
           <xm:sqref>M26</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="100" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Blocked"</xm:f>
             <x14:dxf>
               <fill>
@@ -4765,7 +4804,7 @@
           <xm:sqref>M26</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="101" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Pass"</xm:f>
             <x14:dxf>
               <fill>
@@ -4779,7 +4818,7 @@
           <xm:sqref>M26</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="102" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Fail"</xm:f>
             <x14:dxf>
               <fill>
@@ -4793,7 +4832,7 @@
           <xm:sqref>M26</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="103" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Blocked"</xm:f>
             <x14:dxf>
               <fill>
@@ -4807,7 +4846,7 @@
           <xm:sqref>M26</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="104" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Pass"</xm:f>
             <x14:dxf>
               <fill>
@@ -4821,7 +4860,7 @@
           <xm:sqref>M26</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="105" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Fail"</xm:f>
             <x14:dxf>
               <fill>
@@ -4835,7 +4874,7 @@
           <xm:sqref>M26</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="106" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Blocked"</xm:f>
             <x14:dxf>
               <fill>
@@ -4849,7 +4888,7 @@
           <xm:sqref>M26</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="107" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Pass"</xm:f>
             <x14:dxf>
               <fill>
@@ -4863,7 +4902,7 @@
           <xm:sqref>M26</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="108" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Fail"</xm:f>
             <x14:dxf>
               <fill>
@@ -4877,7 +4916,7 @@
           <xm:sqref>M26</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="109" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Blocked"</xm:f>
             <x14:dxf>
               <fill>
@@ -4891,7 +4930,7 @@
           <xm:sqref>M26</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="110" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Pass"</xm:f>
             <x14:dxf>
               <fill>
@@ -4905,7 +4944,7 @@
           <xm:sqref>M26</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="111" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Fail"</xm:f>
             <x14:dxf>
               <fill>
@@ -4919,7 +4958,7 @@
           <xm:sqref>M26</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="112" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Blocked"</xm:f>
             <x14:dxf>
               <fill>
@@ -4933,7 +4972,7 @@
           <xm:sqref>M26</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="113" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Pass"</xm:f>
             <x14:dxf>
               <fill>
@@ -4947,7 +4986,7 @@
           <xm:sqref>M26</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="114" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Fail"</xm:f>
             <x14:dxf>
               <fill>
@@ -4961,7 +5000,7 @@
           <xm:sqref>M26</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+          <x14:cfRule type="cellIs" priority="115" aboveAverage="0" operator="equal" rank="0" text="">
             <xm:f>"Blocked"</xm:f>
             <x14:dxf>
               <fill>
@@ -4978,7 +5017,7 @@
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="9" disablePrompts="0">
-        <x14:dataValidation xr:uid="{1C1F83F4-DCAD-4900-9F08-46A0ED2A5702}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
+        <x14:dataValidation xr:uid="{6ADE8671-DDC5-4207-A0BA-BA3AC60B27C8}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
           <x14:formula1>
             <xm:f>"Not Run,Pass,Fail,Blocked,Skipped"</xm:f>
           </x14:formula1>
@@ -4987,7 +5026,7 @@
           </x14:formula2>
           <xm:sqref>M2:M16</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{29D6183F-1C3D-484B-A87B-EBF39946C35D}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
+        <x14:dataValidation xr:uid="{5476ACE9-6595-41E2-959D-B7ECEBE1FAE0}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
           <x14:formula1>
             <xm:f>"Not Run,Pass,Fail,Blocked,Skipped"</xm:f>
           </x14:formula1>
@@ -4996,7 +5035,7 @@
           </x14:formula2>
           <xm:sqref>M18</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{701A93A6-75E2-45E9-8984-1EB581FEC577}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
+        <x14:dataValidation xr:uid="{5BA9EDB5-FAA8-442E-A272-829D481337B1}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
           <x14:formula1>
             <xm:f>"Not Run,Pass,Fail,Blocked,Skipped"</xm:f>
           </x14:formula1>
@@ -5005,7 +5044,7 @@
           </x14:formula2>
           <xm:sqref>M19</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{412503E6-BDBA-4824-ACE6-C26B86AF95DE}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
+        <x14:dataValidation xr:uid="{0D161274-75A8-4376-A47B-6231B5293CDC}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
           <x14:formula1>
             <xm:f>"Not Run,Pass,Fail,Blocked,Skipped"</xm:f>
           </x14:formula1>
@@ -5014,7 +5053,7 @@
           </x14:formula2>
           <xm:sqref>M20</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{3509C0B1-35D4-471B-A8FD-4F06F0E94DB4}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
+        <x14:dataValidation xr:uid="{26EF87F1-9D25-4E71-99D3-C228C0AD0ABA}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
           <x14:formula1>
             <xm:f>"Not Run,Pass,Fail,Blocked,Skipped"</xm:f>
           </x14:formula1>
@@ -5023,7 +5062,7 @@
           </x14:formula2>
           <xm:sqref>M21</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{54381B46-38F3-4496-A12F-77B4E4F9B3AA}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
+        <x14:dataValidation xr:uid="{46B6FE8D-85BF-4C62-A2BB-31E5587AF890}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
           <x14:formula1>
             <xm:f>"Not Run,Pass,Fail,Blocked,Skipped"</xm:f>
           </x14:formula1>
@@ -5032,7 +5071,7 @@
           </x14:formula2>
           <xm:sqref>M23</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{2FF03370-1799-4664-8B94-7F26FF05D694}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
+        <x14:dataValidation xr:uid="{4F431A2B-2B6C-4F38-BDA1-E79BD29CC40E}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
           <x14:formula1>
             <xm:f>"Not Run,Pass,Fail,Blocked,Skipped"</xm:f>
           </x14:formula1>
@@ -5041,7 +5080,7 @@
           </x14:formula2>
           <xm:sqref>M24</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{15F726E3-4587-4069-8DFF-84B80575A152}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
+        <x14:dataValidation xr:uid="{4D05FD78-F0B5-4334-8BE9-89F61249A41C}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
           <x14:formula1>
             <xm:f>"Not Run,Pass,Fail,Blocked,Skipped"</xm:f>
           </x14:formula1>
@@ -5050,7 +5089,7 @@
           </x14:formula2>
           <xm:sqref>M25</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{05AD8129-44E8-4D45-B5BF-17BD74FCB627}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
+        <x14:dataValidation xr:uid="{7C9A1D03-7531-49DB-8965-ED0D4A458743}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
           <x14:formula1>
             <xm:f>"Not Run,Pass,Fail,Blocked,Skipped"</xm:f>
           </x14:formula1>
@@ -5089,829 +5128,829 @@
   </cols>
   <sheetData>
     <row r="1" ht="23.850000000000001" customHeight="1">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="H1" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C1" s="12" t="s">
+      <c r="I1" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="J1" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="K1" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="L1" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="M1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="N1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="O1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="J1" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="K1" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="L1" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="M1" s="12" t="s">
+    </row>
+    <row r="2" ht="46.25" customHeight="1">
+      <c r="A2" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>190</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>191</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G2" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="H2" s="15" t="s">
+        <v>192</v>
+      </c>
+      <c r="I2" s="15" t="s">
+        <v>193</v>
+      </c>
+      <c r="J2" s="15" t="s">
+        <v>194</v>
+      </c>
+      <c r="K2" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L2" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="M2" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="N2" s="15"/>
+      <c r="O2" s="15"/>
+    </row>
+    <row r="3" ht="46.25" customHeight="1">
+      <c r="A3" s="15" t="s">
+        <v>196</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>190</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>197</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="H3" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="I3" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="J3" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="K3" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L3" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="M3" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="N3" s="15"/>
+      <c r="O3" s="15"/>
+    </row>
+    <row r="4" ht="35.049999999999997" customHeight="1">
+      <c r="A4" s="15" t="s">
+        <v>202</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>190</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="N1" s="12" t="s">
+      <c r="G4" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="O1" s="12" t="s">
+      <c r="H4" s="15" t="s">
+        <v>204</v>
+      </c>
+      <c r="I4" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="J4" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="K4" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L4" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="M4" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="N4" s="15"/>
+      <c r="O4" s="15"/>
+    </row>
+    <row r="5" ht="35.049999999999997" customHeight="1">
+      <c r="A5" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>190</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>208</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="G5" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="H5" s="15" t="s">
+        <v>209</v>
+      </c>
+      <c r="I5" s="15" t="s">
+        <v>210</v>
+      </c>
+      <c r="J5" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="K5" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L5" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="M5" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="N5" s="15"/>
+      <c r="O5" s="15" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="6" ht="23.850000000000001" customHeight="1">
+      <c r="A6" s="15" t="s">
+        <v>213</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>214</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>215</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G6" s="15" t="s">
+        <v>216</v>
+      </c>
+      <c r="H6" s="15" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="2" ht="46.25" customHeight="1">
-      <c r="A2" s="13" t="s">
+      <c r="I6" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="J6" s="15" t="s">
+        <v>218</v>
+      </c>
+      <c r="K6" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L6" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="M6" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="N6" s="15"/>
+      <c r="O6" s="15"/>
+    </row>
+    <row r="7" ht="23.850000000000001" customHeight="1">
+      <c r="A7" s="15" t="s">
+        <v>220</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>214</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>221</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7" s="15" t="s">
+        <v>216</v>
+      </c>
+      <c r="H7" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="I7" s="15" t="s">
+        <v>222</v>
+      </c>
+      <c r="J7" s="15" t="s">
+        <v>223</v>
+      </c>
+      <c r="K7" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L7" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="M7" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="N7" s="15"/>
+      <c r="O7" s="15"/>
+    </row>
+    <row r="8" ht="23.850000000000001" customHeight="1">
+      <c r="A8" s="15" t="s">
+        <v>224</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>225</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="G8" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="H8" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="I8" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="J8" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="K8" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L8" s="15" t="s">
+        <v>230</v>
+      </c>
+      <c r="M8" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="N8" s="15"/>
+      <c r="O8" s="15"/>
+    </row>
+    <row r="9" ht="57.450000000000003" customHeight="1">
+      <c r="A9" s="15" t="s">
+        <v>231</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>225</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>232</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="G9" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="H9" s="15" t="s">
+        <v>233</v>
+      </c>
+      <c r="I9" s="15" t="s">
+        <v>234</v>
+      </c>
+      <c r="J9" s="15" t="s">
+        <v>235</v>
+      </c>
+      <c r="K9" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L9" s="15" t="s">
+        <v>230</v>
+      </c>
+      <c r="M9" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="N9" s="15"/>
+      <c r="O9" s="15"/>
+    </row>
+    <row r="10" ht="35.049999999999997" customHeight="1">
+      <c r="A10" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>238</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="G10" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="H10" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="I10" s="15" t="s">
+        <v>240</v>
+      </c>
+      <c r="J10" s="15" t="s">
+        <v>241</v>
+      </c>
+      <c r="K10" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L10" s="15" t="s">
+        <v>242</v>
+      </c>
+      <c r="M10" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="N10" s="15"/>
+      <c r="O10" s="15"/>
+    </row>
+    <row r="11" ht="35.049999999999997" customHeight="1">
+      <c r="A11" s="15" t="s">
+        <v>243</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>244</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="G11" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="H11" s="15" t="s">
+        <v>245</v>
+      </c>
+      <c r="I11" s="15" t="s">
+        <v>246</v>
+      </c>
+      <c r="J11" s="15" t="s">
+        <v>247</v>
+      </c>
+      <c r="K11" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L11" s="15" t="s">
+        <v>242</v>
+      </c>
+      <c r="M11" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="N11" s="15"/>
+      <c r="O11" s="15"/>
+    </row>
+    <row r="12" ht="35.049999999999997" customHeight="1">
+      <c r="A12" s="15" t="s">
+        <v>248</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>249</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="G12" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="H12" s="15" t="s">
+        <v>250</v>
+      </c>
+      <c r="I12" s="15" t="s">
+        <v>251</v>
+      </c>
+      <c r="J12" s="15" t="s">
+        <v>252</v>
+      </c>
+      <c r="K12" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L12" s="15" t="s">
+        <v>242</v>
+      </c>
+      <c r="M12" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="N12" s="15"/>
+      <c r="O12" s="15"/>
+    </row>
+    <row r="13" ht="23.850000000000001" customHeight="1">
+      <c r="A13" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>255</v>
+      </c>
+      <c r="E13" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="G13" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="H13" s="15" t="s">
+        <v>233</v>
+      </c>
+      <c r="I13" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="J13" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="K13" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="L13" s="15" t="s">
+        <v>259</v>
+      </c>
+      <c r="M13" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="N13" s="15"/>
+      <c r="O13" s="15"/>
+    </row>
+    <row r="14" ht="23.850000000000001" customHeight="1">
+      <c r="A14" s="15" t="s">
+        <v>260</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>261</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G14" s="15" t="s">
+        <v>262</v>
+      </c>
+      <c r="H14" s="15" t="s">
+        <v>263</v>
+      </c>
+      <c r="I14" s="15" t="s">
+        <v>264</v>
+      </c>
+      <c r="J14" s="15" t="s">
+        <v>265</v>
+      </c>
+      <c r="K14" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="L14" s="15" t="s">
+        <v>266</v>
+      </c>
+      <c r="M14" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="N14" s="15"/>
+      <c r="O14" s="15"/>
+    </row>
+    <row r="15" ht="23.850000000000001" customHeight="1">
+      <c r="A15" s="15" t="s">
+        <v>267</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>214</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>268</v>
+      </c>
+      <c r="E15" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="G15" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="H15" s="15" t="s">
+        <v>269</v>
+      </c>
+      <c r="I15" s="15" t="s">
+        <v>270</v>
+      </c>
+      <c r="J15" s="15" t="s">
+        <v>271</v>
+      </c>
+      <c r="K15" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="L15" s="15" t="s">
+        <v>266</v>
+      </c>
+      <c r="M15" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="N15" s="15"/>
+      <c r="O15" s="15"/>
+    </row>
+    <row r="16" ht="35.049999999999997" customHeight="1">
+      <c r="A16" s="15" t="s">
+        <v>272</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>190</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>273</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="G16" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="H16" s="15" t="s">
+        <v>274</v>
+      </c>
+      <c r="I16" s="15" t="s">
+        <v>275</v>
+      </c>
+      <c r="J16" s="15" t="s">
+        <v>276</v>
+      </c>
+      <c r="K16" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="L16" s="15" t="s">
         <v>195</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="M16" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="N16" s="15"/>
+      <c r="O16" s="15" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="17" ht="23.850000000000001" customHeight="1">
+      <c r="A17" s="15" t="s">
+        <v>278</v>
+      </c>
+      <c r="B17" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="13" t="s">
-        <v>196</v>
-      </c>
-      <c r="D2" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="E2" s="14" t="s">
+      <c r="C17" s="15" t="s">
+        <v>214</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>279</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="F17" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="G17" s="15" t="s">
+        <v>280</v>
+      </c>
+      <c r="H17" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="I17" s="15" t="s">
+        <v>281</v>
+      </c>
+      <c r="J17" s="15" t="s">
+        <v>282</v>
+      </c>
+      <c r="K17" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L17" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="M17" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="N17" s="15"/>
+      <c r="O17" s="15"/>
+    </row>
+    <row r="18" ht="35.049999999999997" customHeight="1">
+      <c r="A18" s="15" t="s">
+        <v>283</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>190</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>284</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="F18" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="G18" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="H18" s="15" t="s">
+        <v>233</v>
+      </c>
+      <c r="I18" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="J18" s="15" t="s">
+        <v>286</v>
+      </c>
+      <c r="K18" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L18" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="M18" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="N18" s="15"/>
+      <c r="O18" s="15"/>
+    </row>
+    <row r="19" ht="46.25" customHeight="1">
+      <c r="A19" s="15" t="s">
+        <v>287</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>288</v>
+      </c>
+      <c r="E19" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="G2" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="H2" s="13" t="s">
-        <v>198</v>
-      </c>
-      <c r="I2" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="J2" s="13" t="s">
-        <v>200</v>
-      </c>
-      <c r="K2" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="L2" s="13" t="s">
-        <v>201</v>
-      </c>
-      <c r="M2" s="13" t="s">
+      <c r="F19" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="G19" s="15" t="s">
+        <v>289</v>
+      </c>
+      <c r="H19" s="15" t="s">
+        <v>290</v>
+      </c>
+      <c r="I19" s="15" t="s">
+        <v>291</v>
+      </c>
+      <c r="J19" s="15" t="s">
+        <v>292</v>
+      </c>
+      <c r="K19" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="L19" s="15" t="s">
+        <v>266</v>
+      </c>
+      <c r="M19" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="N2" s="13"/>
-      <c r="O2" s="13"/>
-    </row>
-    <row r="3" ht="46.25" customHeight="1">
-      <c r="A3" s="13" t="s">
-        <v>202</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>196</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>203</v>
-      </c>
-      <c r="E3" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="G3" s="13" t="s">
-        <v>204</v>
-      </c>
-      <c r="H3" s="13" t="s">
-        <v>205</v>
-      </c>
-      <c r="I3" s="13" t="s">
-        <v>206</v>
-      </c>
-      <c r="J3" s="13" t="s">
-        <v>207</v>
-      </c>
-      <c r="K3" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="L3" s="13" t="s">
-        <v>201</v>
-      </c>
-      <c r="M3" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="N3" s="13"/>
-      <c r="O3" s="13"/>
-    </row>
-    <row r="4" ht="35.049999999999997" customHeight="1">
-      <c r="A4" s="13" t="s">
-        <v>208</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>196</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>209</v>
-      </c>
-      <c r="E4" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="G4" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="H4" s="13" t="s">
-        <v>210</v>
-      </c>
-      <c r="I4" s="13" t="s">
-        <v>211</v>
-      </c>
-      <c r="J4" s="13" t="s">
-        <v>212</v>
-      </c>
-      <c r="K4" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="L4" s="13" t="s">
-        <v>201</v>
-      </c>
-      <c r="M4" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="N4" s="13"/>
-      <c r="O4" s="13"/>
-    </row>
-    <row r="5" ht="35.049999999999997" customHeight="1">
-      <c r="A5" s="13" t="s">
-        <v>213</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>196</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>214</v>
-      </c>
-      <c r="E5" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="G5" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="H5" s="13" t="s">
-        <v>215</v>
-      </c>
-      <c r="I5" s="13" t="s">
-        <v>216</v>
-      </c>
-      <c r="J5" s="13" t="s">
-        <v>217</v>
-      </c>
-      <c r="K5" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="L5" s="13" t="s">
-        <v>201</v>
-      </c>
-      <c r="M5" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="N5" s="13"/>
-      <c r="O5" s="13" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="6" ht="23.850000000000001" customHeight="1">
-      <c r="A6" s="13" t="s">
-        <v>219</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>220</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>221</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="G6" s="13" t="s">
-        <v>222</v>
-      </c>
-      <c r="H6" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="I6" s="13" t="s">
-        <v>223</v>
-      </c>
-      <c r="J6" s="13" t="s">
-        <v>224</v>
-      </c>
-      <c r="K6" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="L6" s="13" t="s">
-        <v>225</v>
-      </c>
-      <c r="M6" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="N6" s="13"/>
-      <c r="O6" s="13"/>
-    </row>
-    <row r="7" ht="23.850000000000001" customHeight="1">
-      <c r="A7" s="13" t="s">
-        <v>226</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>220</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>227</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="G7" s="13" t="s">
-        <v>222</v>
-      </c>
-      <c r="H7" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="I7" s="13" t="s">
-        <v>228</v>
-      </c>
-      <c r="J7" s="13" t="s">
-        <v>229</v>
-      </c>
-      <c r="K7" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="L7" s="13" t="s">
-        <v>225</v>
-      </c>
-      <c r="M7" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="N7" s="13"/>
-      <c r="O7" s="13"/>
-    </row>
-    <row r="8" ht="23.850000000000001" customHeight="1">
-      <c r="A8" s="13" t="s">
-        <v>230</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>231</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>232</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="G8" s="13" t="s">
-        <v>233</v>
-      </c>
-      <c r="H8" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="I8" s="13" t="s">
-        <v>234</v>
-      </c>
-      <c r="J8" s="13" t="s">
-        <v>235</v>
-      </c>
-      <c r="K8" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="L8" s="13" t="s">
-        <v>236</v>
-      </c>
-      <c r="M8" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="N8" s="13"/>
-      <c r="O8" s="13"/>
-    </row>
-    <row r="9" ht="57.450000000000003" customHeight="1">
-      <c r="A9" s="13" t="s">
-        <v>237</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>231</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>238</v>
-      </c>
-      <c r="E9" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="G9" s="13" t="s">
-        <v>204</v>
-      </c>
-      <c r="H9" s="13" t="s">
-        <v>239</v>
-      </c>
-      <c r="I9" s="13" t="s">
-        <v>240</v>
-      </c>
-      <c r="J9" s="13" t="s">
-        <v>241</v>
-      </c>
-      <c r="K9" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="L9" s="13" t="s">
-        <v>236</v>
-      </c>
-      <c r="M9" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="N9" s="13"/>
-      <c r="O9" s="13"/>
-    </row>
-    <row r="10" ht="35.049999999999997" customHeight="1">
-      <c r="A10" s="13" t="s">
-        <v>242</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>243</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>244</v>
-      </c>
-      <c r="E10" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="G10" s="13" t="s">
-        <v>245</v>
-      </c>
-      <c r="H10" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="I10" s="13" t="s">
-        <v>246</v>
-      </c>
-      <c r="J10" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="K10" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="L10" s="13" t="s">
-        <v>248</v>
-      </c>
-      <c r="M10" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="N10" s="13"/>
-      <c r="O10" s="13"/>
-    </row>
-    <row r="11" ht="35.049999999999997" customHeight="1">
-      <c r="A11" s="13" t="s">
-        <v>249</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>243</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>250</v>
-      </c>
-      <c r="E11" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="G11" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="H11" s="13" t="s">
-        <v>251</v>
-      </c>
-      <c r="I11" s="13" t="s">
-        <v>252</v>
-      </c>
-      <c r="J11" s="13" t="s">
-        <v>253</v>
-      </c>
-      <c r="K11" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="L11" s="13" t="s">
-        <v>248</v>
-      </c>
-      <c r="M11" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="N11" s="13"/>
-      <c r="O11" s="13"/>
-    </row>
-    <row r="12" ht="35.049999999999997" customHeight="1">
-      <c r="A12" s="13" t="s">
-        <v>254</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>243</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>255</v>
-      </c>
-      <c r="E12" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G12" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="H12" s="13" t="s">
-        <v>256</v>
-      </c>
-      <c r="I12" s="13" t="s">
-        <v>257</v>
-      </c>
-      <c r="J12" s="13" t="s">
-        <v>258</v>
-      </c>
-      <c r="K12" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="L12" s="13" t="s">
-        <v>248</v>
-      </c>
-      <c r="M12" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="N12" s="13"/>
-      <c r="O12" s="13"/>
-    </row>
-    <row r="13" ht="23.850000000000001" customHeight="1">
-      <c r="A13" s="13" t="s">
-        <v>259</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>260</v>
-      </c>
-      <c r="D13" s="13" t="s">
-        <v>261</v>
-      </c>
-      <c r="E13" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="F13" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="G13" s="13" t="s">
-        <v>262</v>
-      </c>
-      <c r="H13" s="13" t="s">
-        <v>239</v>
-      </c>
-      <c r="I13" s="13" t="s">
-        <v>263</v>
-      </c>
-      <c r="J13" s="13" t="s">
-        <v>264</v>
-      </c>
-      <c r="K13" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="L13" s="13" t="s">
-        <v>265</v>
-      </c>
-      <c r="M13" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="N13" s="13"/>
-      <c r="O13" s="13"/>
-    </row>
-    <row r="14" ht="23.850000000000001" customHeight="1">
-      <c r="A14" s="13" t="s">
-        <v>266</v>
-      </c>
-      <c r="B14" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>260</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>267</v>
-      </c>
-      <c r="E14" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="G14" s="13" t="s">
-        <v>268</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>269</v>
-      </c>
-      <c r="I14" s="13" t="s">
-        <v>270</v>
-      </c>
-      <c r="J14" s="13" t="s">
-        <v>271</v>
-      </c>
-      <c r="K14" s="13" t="s">
-        <v>188</v>
-      </c>
-      <c r="L14" s="13" t="s">
-        <v>272</v>
-      </c>
-      <c r="M14" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="N14" s="13"/>
-      <c r="O14" s="13"/>
-    </row>
-    <row r="15" ht="23.850000000000001" customHeight="1">
-      <c r="A15" s="13" t="s">
-        <v>273</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>220</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>274</v>
-      </c>
-      <c r="E15" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G15" s="13" t="s">
-        <v>245</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="I15" s="13" t="s">
-        <v>276</v>
-      </c>
-      <c r="J15" s="13" t="s">
-        <v>277</v>
-      </c>
-      <c r="K15" s="13" t="s">
-        <v>188</v>
-      </c>
-      <c r="L15" s="13" t="s">
-        <v>272</v>
-      </c>
-      <c r="M15" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="N15" s="13"/>
-      <c r="O15" s="13"/>
-    </row>
-    <row r="16" ht="35.049999999999997" customHeight="1">
-      <c r="A16" s="13" t="s">
-        <v>278</v>
-      </c>
-      <c r="B16" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>196</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>279</v>
-      </c>
-      <c r="E16" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="F16" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G16" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="H16" s="13" t="s">
-        <v>280</v>
-      </c>
-      <c r="I16" s="13" t="s">
-        <v>281</v>
-      </c>
-      <c r="J16" s="13" t="s">
-        <v>282</v>
-      </c>
-      <c r="K16" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="L16" s="13" t="s">
-        <v>201</v>
-      </c>
-      <c r="M16" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="N16" s="13"/>
-      <c r="O16" s="13" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="17" ht="23.850000000000001" customHeight="1">
-      <c r="A17" s="13" t="s">
-        <v>284</v>
-      </c>
-      <c r="B17" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" s="13" t="s">
-        <v>220</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>285</v>
-      </c>
-      <c r="E17" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="F17" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G17" s="13" t="s">
-        <v>286</v>
-      </c>
-      <c r="H17" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="I17" s="13" t="s">
-        <v>287</v>
-      </c>
-      <c r="J17" s="13" t="s">
-        <v>288</v>
-      </c>
-      <c r="K17" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="L17" s="13" t="s">
-        <v>225</v>
-      </c>
-      <c r="M17" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="N17" s="13"/>
-      <c r="O17" s="13"/>
-    </row>
-    <row r="18" ht="35.049999999999997" customHeight="1">
-      <c r="A18" s="13" t="s">
-        <v>289</v>
-      </c>
-      <c r="B18" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C18" s="13" t="s">
-        <v>196</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>290</v>
-      </c>
-      <c r="E18" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="F18" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="G18" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="H18" s="13" t="s">
-        <v>239</v>
-      </c>
-      <c r="I18" s="13" t="s">
-        <v>291</v>
-      </c>
-      <c r="J18" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="K18" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="L18" s="13" t="s">
-        <v>201</v>
-      </c>
-      <c r="M18" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="N18" s="13"/>
-      <c r="O18" s="13"/>
-    </row>
-    <row r="19" ht="46.25" customHeight="1">
-      <c r="A19" s="13" t="s">
-        <v>293</v>
-      </c>
-      <c r="B19" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C19" s="13" t="s">
-        <v>188</v>
-      </c>
-      <c r="D19" s="13" t="s">
-        <v>294</v>
-      </c>
-      <c r="E19" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="F19" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="G19" s="13" t="s">
-        <v>295</v>
-      </c>
-      <c r="H19" s="13" t="s">
-        <v>296</v>
-      </c>
-      <c r="I19" s="13" t="s">
-        <v>297</v>
-      </c>
-      <c r="J19" s="13" t="s">
-        <v>298</v>
-      </c>
-      <c r="K19" s="13" t="s">
-        <v>188</v>
-      </c>
-      <c r="L19" s="13" t="s">
-        <v>272</v>
-      </c>
-      <c r="M19" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="N19" s="13"/>
-      <c r="O19" s="13"/>
+      <c r="N19" s="15"/>
+      <c r="O19" s="15"/>
     </row>
     <row r="20" ht="46.25" customHeight="1"/>
     <row r="21" ht="35.049999999999997" customHeight="1"/>
@@ -5982,7 +6021,7 @@
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1" disablePrompts="0">
-        <x14:dataValidation xr:uid="{49C9940B-44B3-475D-B2CB-BD180AEDD24E}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
+        <x14:dataValidation xr:uid="{249AFDEA-C53C-44E5-B19A-4A3831F35E64}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
           <x14:formula1>
             <xm:f>"Not Run,Pass,Fail,Blocked,Skipped"</xm:f>
           </x14:formula1>
@@ -6018,659 +6057,659 @@
   </cols>
   <sheetData>
     <row r="1" ht="23.850000000000001" customHeight="1">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="H1" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C1" s="12" t="s">
+      <c r="I1" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="J1" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="K1" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="L1" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="M1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="N1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="O1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="J1" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="K1" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="L1" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="M1" s="12" t="s">
+    </row>
+    <row r="2" ht="23.850000000000001" customHeight="1">
+      <c r="A2" s="15" t="s">
+        <v>293</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>294</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>295</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="N1" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="O1" s="12" t="s">
+      <c r="G2" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="H2" s="15" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="2" ht="23.850000000000001" customHeight="1">
-      <c r="A2" s="13" t="s">
+      <c r="I2" s="15" t="s">
+        <v>296</v>
+      </c>
+      <c r="J2" s="15" t="s">
+        <v>297</v>
+      </c>
+      <c r="K2" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L2" s="15" t="s">
+        <v>298</v>
+      </c>
+      <c r="M2" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="N2" s="15"/>
+      <c r="O2" s="15"/>
+    </row>
+    <row r="3" ht="68.650000000000006" customHeight="1">
+      <c r="A3" s="15" t="s">
         <v>299</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B3" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C3" s="15" t="s">
+        <v>294</v>
+      </c>
+      <c r="D3" s="15" t="s">
         <v>300</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="E3" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="H3" s="15" t="s">
         <v>301</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="I3" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="J3" s="15" t="s">
+        <v>303</v>
+      </c>
+      <c r="K3" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L3" s="15" t="s">
+        <v>298</v>
+      </c>
+      <c r="M3" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="N3" s="15"/>
+      <c r="O3" s="15"/>
+    </row>
+    <row r="4" ht="35.049999999999997" customHeight="1">
+      <c r="A4" s="15" t="s">
+        <v>304</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>294</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>305</v>
+      </c>
+      <c r="E4" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="G2" s="13" t="s">
-        <v>245</v>
-      </c>
-      <c r="H2" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="I2" s="13" t="s">
-        <v>302</v>
-      </c>
-      <c r="J2" s="13" t="s">
-        <v>303</v>
-      </c>
-      <c r="K2" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="L2" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="M2" s="13" t="s">
+      <c r="F4" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="G4" s="15" t="s">
+        <v>216</v>
+      </c>
+      <c r="H4" s="15" t="s">
+        <v>306</v>
+      </c>
+      <c r="I4" s="15" t="s">
+        <v>307</v>
+      </c>
+      <c r="J4" s="15" t="s">
+        <v>308</v>
+      </c>
+      <c r="K4" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L4" s="15" t="s">
+        <v>298</v>
+      </c>
+      <c r="M4" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="N2" s="13"/>
-      <c r="O2" s="13"/>
-    </row>
-    <row r="3" ht="68.650000000000006" customHeight="1">
-      <c r="A3" s="13" t="s">
-        <v>305</v>
-      </c>
-      <c r="B3" s="13" t="s">
+      <c r="N4" s="15"/>
+      <c r="O4" s="15"/>
+    </row>
+    <row r="5" ht="35.049999999999997" customHeight="1">
+      <c r="A5" s="15" t="s">
+        <v>309</v>
+      </c>
+      <c r="B5" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="13" t="s">
-        <v>300</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>306</v>
-      </c>
-      <c r="E3" s="14" t="s">
+      <c r="C5" s="15" t="s">
+        <v>294</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>310</v>
+      </c>
+      <c r="E5" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="G3" s="13" t="s">
-        <v>245</v>
-      </c>
-      <c r="H3" s="13" t="s">
-        <v>307</v>
-      </c>
-      <c r="I3" s="13" t="s">
-        <v>308</v>
-      </c>
-      <c r="J3" s="13" t="s">
-        <v>309</v>
-      </c>
-      <c r="K3" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="L3" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="M3" s="13" t="s">
+      <c r="F5" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G5" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="H5" s="15" t="s">
+        <v>311</v>
+      </c>
+      <c r="I5" s="15" t="s">
+        <v>312</v>
+      </c>
+      <c r="J5" s="15" t="s">
+        <v>313</v>
+      </c>
+      <c r="K5" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L5" s="15" t="s">
+        <v>298</v>
+      </c>
+      <c r="M5" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="N3" s="13"/>
-      <c r="O3" s="13"/>
-    </row>
-    <row r="4" ht="35.049999999999997" customHeight="1">
-      <c r="A4" s="13" t="s">
-        <v>310</v>
-      </c>
-      <c r="B4" s="13" t="s">
+      <c r="N5" s="15"/>
+      <c r="O5" s="15"/>
+    </row>
+    <row r="6" ht="23.850000000000001" customHeight="1">
+      <c r="A6" s="15" t="s">
+        <v>314</v>
+      </c>
+      <c r="B6" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="13" t="s">
-        <v>300</v>
-      </c>
-      <c r="D4" s="13" t="s">
+      <c r="C6" s="15" t="s">
+        <v>294</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>315</v>
+      </c>
+      <c r="E6" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="G6" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="H6" s="15" t="s">
+        <v>316</v>
+      </c>
+      <c r="I6" s="15" t="s">
+        <v>317</v>
+      </c>
+      <c r="J6" s="15" t="s">
+        <v>318</v>
+      </c>
+      <c r="K6" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L6" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="M6" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="N6" s="15"/>
+      <c r="O6" s="15"/>
+    </row>
+    <row r="7" ht="35.049999999999997" customHeight="1">
+      <c r="A7" s="15" t="s">
+        <v>320</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>294</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>321</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="H7" s="15" t="s">
+        <v>322</v>
+      </c>
+      <c r="I7" s="15" t="s">
+        <v>323</v>
+      </c>
+      <c r="J7" s="15" t="s">
+        <v>324</v>
+      </c>
+      <c r="K7" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L7" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="M7" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="N7" s="15"/>
+      <c r="O7" s="15"/>
+    </row>
+    <row r="8" ht="35.049999999999997" customHeight="1">
+      <c r="A8" s="15" t="s">
+        <v>325</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>294</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>326</v>
+      </c>
+      <c r="E8" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="G8" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="H8" s="15" t="s">
+        <v>327</v>
+      </c>
+      <c r="I8" s="15" t="s">
+        <v>328</v>
+      </c>
+      <c r="J8" s="15" t="s">
+        <v>324</v>
+      </c>
+      <c r="K8" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L8" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="M8" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="N8" s="15"/>
+      <c r="O8" s="15"/>
+    </row>
+    <row r="9" ht="46.25" customHeight="1">
+      <c r="A9" s="15" t="s">
+        <v>329</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>294</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>330</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="G9" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="H9" s="15" t="s">
         <v>311</v>
       </c>
-      <c r="E4" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="G4" s="13" t="s">
-        <v>222</v>
-      </c>
-      <c r="H4" s="13" t="s">
-        <v>312</v>
-      </c>
-      <c r="I4" s="13" t="s">
-        <v>313</v>
-      </c>
-      <c r="J4" s="13" t="s">
-        <v>314</v>
-      </c>
-      <c r="K4" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="L4" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="M4" s="13" t="s">
+      <c r="I9" s="15" t="s">
+        <v>331</v>
+      </c>
+      <c r="J9" s="15" t="s">
+        <v>332</v>
+      </c>
+      <c r="K9" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L9" s="15" t="s">
+        <v>298</v>
+      </c>
+      <c r="M9" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="N4" s="13"/>
-      <c r="O4" s="13"/>
-    </row>
-    <row r="5" ht="35.049999999999997" customHeight="1">
-      <c r="A5" s="13" t="s">
-        <v>315</v>
-      </c>
-      <c r="B5" s="13" t="s">
+      <c r="N9" s="15"/>
+      <c r="O9" s="15"/>
+    </row>
+    <row r="10" ht="35.049999999999997" customHeight="1">
+      <c r="A10" s="15" t="s">
+        <v>333</v>
+      </c>
+      <c r="B10" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="13" t="s">
-        <v>300</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>316</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="G5" s="13" t="s">
-        <v>245</v>
-      </c>
-      <c r="H5" s="13" t="s">
-        <v>317</v>
-      </c>
-      <c r="I5" s="13" t="s">
-        <v>318</v>
-      </c>
-      <c r="J5" s="13" t="s">
+      <c r="C10" s="15" t="s">
+        <v>294</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>334</v>
+      </c>
+      <c r="E10" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="G10" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="H10" s="15" t="s">
+        <v>335</v>
+      </c>
+      <c r="I10" s="15" t="s">
+        <v>336</v>
+      </c>
+      <c r="J10" s="15" t="s">
+        <v>337</v>
+      </c>
+      <c r="K10" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L10" s="15" t="s">
         <v>319</v>
       </c>
-      <c r="K5" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="L5" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="M5" s="13" t="s">
+      <c r="M10" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="N5" s="13"/>
-      <c r="O5" s="13"/>
-    </row>
-    <row r="6" ht="23.850000000000001" customHeight="1">
-      <c r="A6" s="13" t="s">
-        <v>320</v>
-      </c>
-      <c r="B6" s="13" t="s">
+      <c r="N10" s="15"/>
+      <c r="O10" s="15" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="11" ht="35.049999999999997" customHeight="1">
+      <c r="A11" s="15" t="s">
+        <v>339</v>
+      </c>
+      <c r="B11" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="13" t="s">
-        <v>300</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>321</v>
-      </c>
-      <c r="E6" s="16" t="s">
+      <c r="C11" s="15" t="s">
+        <v>294</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>340</v>
+      </c>
+      <c r="E11" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="G6" s="13" t="s">
-        <v>245</v>
-      </c>
-      <c r="H6" s="13" t="s">
-        <v>322</v>
-      </c>
-      <c r="I6" s="13" t="s">
-        <v>323</v>
-      </c>
-      <c r="J6" s="13" t="s">
-        <v>324</v>
-      </c>
-      <c r="K6" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="L6" s="13" t="s">
-        <v>325</v>
-      </c>
-      <c r="M6" s="13" t="s">
+      <c r="F11" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="G11" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="H11" s="15" t="s">
+        <v>341</v>
+      </c>
+      <c r="I11" s="15" t="s">
+        <v>342</v>
+      </c>
+      <c r="J11" s="15" t="s">
+        <v>343</v>
+      </c>
+      <c r="K11" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L11" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="M11" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="N6" s="13"/>
-      <c r="O6" s="13"/>
-    </row>
-    <row r="7" ht="35.049999999999997" customHeight="1">
-      <c r="A7" s="13" t="s">
-        <v>326</v>
-      </c>
-      <c r="B7" s="13" t="s">
+      <c r="N11" s="15"/>
+      <c r="O11" s="15" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="12" ht="35.049999999999997" customHeight="1">
+      <c r="A12" s="15" t="s">
+        <v>344</v>
+      </c>
+      <c r="B12" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="13" t="s">
-        <v>300</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>327</v>
-      </c>
-      <c r="E7" s="16" t="s">
+      <c r="C12" s="15" t="s">
+        <v>294</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>345</v>
+      </c>
+      <c r="E12" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="F7" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="G7" s="13" t="s">
-        <v>245</v>
-      </c>
-      <c r="H7" s="13" t="s">
-        <v>328</v>
-      </c>
-      <c r="I7" s="13" t="s">
-        <v>329</v>
-      </c>
-      <c r="J7" s="13" t="s">
-        <v>330</v>
-      </c>
-      <c r="K7" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="L7" s="13" t="s">
-        <v>325</v>
-      </c>
-      <c r="M7" s="13" t="s">
+      <c r="F12" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="G12" s="15" t="s">
+        <v>346</v>
+      </c>
+      <c r="H12" s="15" t="s">
+        <v>311</v>
+      </c>
+      <c r="I12" s="15" t="s">
+        <v>347</v>
+      </c>
+      <c r="J12" s="15" t="s">
+        <v>348</v>
+      </c>
+      <c r="K12" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L12" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="M12" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="N7" s="13"/>
-      <c r="O7" s="13"/>
-    </row>
-    <row r="8" ht="35.049999999999997" customHeight="1">
-      <c r="A8" s="13" t="s">
-        <v>331</v>
-      </c>
-      <c r="B8" s="13" t="s">
+      <c r="N12" s="15"/>
+      <c r="O12" s="15" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="13" ht="23.850000000000001" customHeight="1">
+      <c r="A13" s="15" t="s">
+        <v>350</v>
+      </c>
+      <c r="B13" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="13" t="s">
-        <v>300</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>332</v>
-      </c>
-      <c r="E8" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="G8" s="13" t="s">
-        <v>245</v>
-      </c>
-      <c r="H8" s="13" t="s">
-        <v>333</v>
-      </c>
-      <c r="I8" s="13" t="s">
-        <v>334</v>
-      </c>
-      <c r="J8" s="13" t="s">
-        <v>330</v>
-      </c>
-      <c r="K8" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="L8" s="13" t="s">
-        <v>325</v>
-      </c>
-      <c r="M8" s="13" t="s">
+      <c r="C13" s="15" t="s">
+        <v>294</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>351</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="G13" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="H13" s="15" t="s">
+        <v>352</v>
+      </c>
+      <c r="I13" s="15" t="s">
+        <v>353</v>
+      </c>
+      <c r="J13" s="15" t="s">
+        <v>354</v>
+      </c>
+      <c r="K13" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L13" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="M13" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="N8" s="13"/>
-      <c r="O8" s="13"/>
-    </row>
-    <row r="9" ht="46.25" customHeight="1">
-      <c r="A9" s="13" t="s">
-        <v>335</v>
-      </c>
-      <c r="B9" s="13" t="s">
+      <c r="N13" s="15"/>
+      <c r="O13" s="15"/>
+    </row>
+    <row r="14" ht="23.850000000000001" customHeight="1">
+      <c r="A14" s="15" t="s">
+        <v>355</v>
+      </c>
+      <c r="B14" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="13" t="s">
-        <v>300</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>336</v>
-      </c>
-      <c r="E9" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G9" s="13" t="s">
-        <v>245</v>
-      </c>
-      <c r="H9" s="13" t="s">
-        <v>317</v>
-      </c>
-      <c r="I9" s="13" t="s">
-        <v>337</v>
-      </c>
-      <c r="J9" s="13" t="s">
-        <v>338</v>
-      </c>
-      <c r="K9" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="L9" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="M9" s="13" t="s">
+      <c r="C14" s="15" t="s">
+        <v>294</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>356</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="G14" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="H14" s="15" t="s">
+        <v>357</v>
+      </c>
+      <c r="I14" s="15" t="s">
+        <v>358</v>
+      </c>
+      <c r="J14" s="15" t="s">
+        <v>359</v>
+      </c>
+      <c r="K14" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L14" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="M14" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="N9" s="13"/>
-      <c r="O9" s="13"/>
-    </row>
-    <row r="10" ht="35.049999999999997" customHeight="1">
-      <c r="A10" s="13" t="s">
-        <v>339</v>
-      </c>
-      <c r="B10" s="13" t="s">
+      <c r="N14" s="15"/>
+      <c r="O14" s="15"/>
+    </row>
+    <row r="15" ht="35.049999999999997" customHeight="1">
+      <c r="A15" s="15" t="s">
+        <v>360</v>
+      </c>
+      <c r="B15" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="13" t="s">
-        <v>300</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>340</v>
-      </c>
-      <c r="E10" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="G10" s="13" t="s">
-        <v>245</v>
-      </c>
-      <c r="H10" s="13" t="s">
-        <v>341</v>
-      </c>
-      <c r="I10" s="13" t="s">
-        <v>342</v>
-      </c>
-      <c r="J10" s="13" t="s">
-        <v>343</v>
-      </c>
-      <c r="K10" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="L10" s="13" t="s">
-        <v>325</v>
-      </c>
-      <c r="M10" s="13" t="s">
+      <c r="C15" s="15" t="s">
+        <v>225</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>361</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="G15" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="H15" s="15" t="s">
+        <v>311</v>
+      </c>
+      <c r="I15" s="15" t="s">
+        <v>362</v>
+      </c>
+      <c r="J15" s="15" t="s">
+        <v>363</v>
+      </c>
+      <c r="K15" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L15" s="15" t="s">
+        <v>298</v>
+      </c>
+      <c r="M15" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="N10" s="13"/>
-      <c r="O10" s="13" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="11" ht="35.049999999999997" customHeight="1">
-      <c r="A11" s="13" t="s">
-        <v>345</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>300</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>346</v>
-      </c>
-      <c r="E11" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G11" s="13" t="s">
-        <v>245</v>
-      </c>
-      <c r="H11" s="13" t="s">
-        <v>347</v>
-      </c>
-      <c r="I11" s="13" t="s">
-        <v>348</v>
-      </c>
-      <c r="J11" s="13" t="s">
-        <v>349</v>
-      </c>
-      <c r="K11" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="L11" s="13" t="s">
-        <v>325</v>
-      </c>
-      <c r="M11" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="N11" s="13"/>
-      <c r="O11" s="13" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="12" ht="35.049999999999997" customHeight="1">
-      <c r="A12" s="13" t="s">
-        <v>350</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>300</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>351</v>
-      </c>
-      <c r="E12" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="G12" s="13" t="s">
-        <v>352</v>
-      </c>
-      <c r="H12" s="13" t="s">
-        <v>317</v>
-      </c>
-      <c r="I12" s="13" t="s">
-        <v>353</v>
-      </c>
-      <c r="J12" s="13" t="s">
-        <v>354</v>
-      </c>
-      <c r="K12" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="L12" s="13" t="s">
-        <v>325</v>
-      </c>
-      <c r="M12" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="N12" s="13"/>
-      <c r="O12" s="13" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="13" ht="23.850000000000001" customHeight="1">
-      <c r="A13" s="13" t="s">
-        <v>356</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>300</v>
-      </c>
-      <c r="D13" s="13" t="s">
-        <v>357</v>
-      </c>
-      <c r="E13" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G13" s="13" t="s">
-        <v>245</v>
-      </c>
-      <c r="H13" s="13" t="s">
-        <v>358</v>
-      </c>
-      <c r="I13" s="13" t="s">
-        <v>359</v>
-      </c>
-      <c r="J13" s="13" t="s">
-        <v>360</v>
-      </c>
-      <c r="K13" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="L13" s="13" t="s">
-        <v>325</v>
-      </c>
-      <c r="M13" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="N13" s="13"/>
-      <c r="O13" s="13"/>
-    </row>
-    <row r="14" ht="23.850000000000001" customHeight="1">
-      <c r="A14" s="13" t="s">
-        <v>361</v>
-      </c>
-      <c r="B14" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>300</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>362</v>
-      </c>
-      <c r="E14" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="G14" s="13" t="s">
-        <v>245</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>363</v>
-      </c>
-      <c r="I14" s="13" t="s">
-        <v>364</v>
-      </c>
-      <c r="J14" s="13" t="s">
-        <v>365</v>
-      </c>
-      <c r="K14" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="L14" s="13" t="s">
-        <v>325</v>
-      </c>
-      <c r="M14" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="N14" s="13"/>
-      <c r="O14" s="13"/>
-    </row>
-    <row r="15" ht="35.049999999999997" customHeight="1">
-      <c r="A15" s="13" t="s">
-        <v>366</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>231</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>367</v>
-      </c>
-      <c r="E15" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="G15" s="13" t="s">
-        <v>245</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>317</v>
-      </c>
-      <c r="I15" s="13" t="s">
-        <v>368</v>
-      </c>
-      <c r="J15" s="13" t="s">
-        <v>369</v>
-      </c>
-      <c r="K15" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="L15" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="M15" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="N15" s="13"/>
-      <c r="O15" s="13"/>
+      <c r="N15" s="15"/>
+      <c r="O15" s="15"/>
     </row>
     <row r="16" ht="35.049999999999997" customHeight="1"/>
     <row r="17" ht="23.850000000000001" customHeight="1"/>
@@ -6745,7 +6784,7 @@
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1" disablePrompts="0">
-        <x14:dataValidation xr:uid="{05693C4F-E1C2-472E-B7C5-440663D94E2D}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
+        <x14:dataValidation xr:uid="{3E07C439-6CF5-429E-A749-7899EFA7F43D}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
           <x14:formula1>
             <xm:f>"Not Run,Pass,Fail,Blocked,Skipped"</xm:f>
           </x14:formula1>

--- a/00.test_case/Demoblaze_TestCases_Login_Cart.xlsx
+++ b/00.test_case/Demoblaze_TestCases_Login_Cart.xlsx
@@ -4,7 +4,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0" showHorizontalScroll="1" showVerticalScroll="1"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="2" showHorizontalScroll="1" showVerticalScroll="1"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
@@ -947,7 +947,7 @@
     <t>CT-015</t>
   </si>
   <si>
-    <t xml:space="preserve">Add many items (10)</t>
+    <t xml:space="preserve">Add many items (10) or max</t>
   </si>
   <si>
     <t xml:space="preserve">10 x add to cart via API</t>
@@ -957,7 +957,7 @@
 2. Open 'Cart'</t>
   </si>
   <si>
-    <t xml:space="preserve">10 rows listed; total equals sum of prices</t>
+    <t xml:space="preserve">10 (max) rows listed; total equals sum of prices</t>
   </si>
   <si>
     <t xml:space="preserve">Items seeded via API to speed up setup</t>
@@ -2108,7 +2108,7 @@
         <v>0.92</v>
       </c>
       <c r="G18" s="12">
-        <f>1-E18/E11</f>
+        <f t="shared" ref="G18:G20" si="2">1-E18/E11</f>
         <v>1</v>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="B19" s="7">
         <f>COUNTIF(Cart!$M:$M,"Pass")</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C19" s="7">
         <f>COUNTIF(Cart!$M:$M,"Fail")</f>
@@ -2130,15 +2130,15 @@
       </c>
       <c r="E19" s="7">
         <f>COUNTIF(Cart!$M:$M,"Not Run")</f>
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F19" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" s="12">
-        <f>1-E19/E12</f>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
@@ -2166,7 +2166,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="12">
-        <f>1-E20/E13</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -5017,7 +5017,7 @@
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="9" disablePrompts="0">
-        <x14:dataValidation xr:uid="{6ADE8671-DDC5-4207-A0BA-BA3AC60B27C8}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
+        <x14:dataValidation xr:uid="{7D526BDB-C970-4102-88CF-19C2D028DEC3}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
           <x14:formula1>
             <xm:f>"Not Run,Pass,Fail,Blocked,Skipped"</xm:f>
           </x14:formula1>
@@ -5026,7 +5026,7 @@
           </x14:formula2>
           <xm:sqref>M2:M16</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{5476ACE9-6595-41E2-959D-B7ECEBE1FAE0}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
+        <x14:dataValidation xr:uid="{153BD1CA-CFD0-4112-B0C0-0B1B9E57E002}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
           <x14:formula1>
             <xm:f>"Not Run,Pass,Fail,Blocked,Skipped"</xm:f>
           </x14:formula1>
@@ -5035,7 +5035,7 @@
           </x14:formula2>
           <xm:sqref>M18</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{5BA9EDB5-FAA8-442E-A272-829D481337B1}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
+        <x14:dataValidation xr:uid="{10040218-07D9-4C18-A47C-51986CB9FD68}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
           <x14:formula1>
             <xm:f>"Not Run,Pass,Fail,Blocked,Skipped"</xm:f>
           </x14:formula1>
@@ -5044,7 +5044,7 @@
           </x14:formula2>
           <xm:sqref>M19</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{0D161274-75A8-4376-A47B-6231B5293CDC}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
+        <x14:dataValidation xr:uid="{391196E1-7DD8-42D8-B7E3-A7F2A5781A84}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
           <x14:formula1>
             <xm:f>"Not Run,Pass,Fail,Blocked,Skipped"</xm:f>
           </x14:formula1>
@@ -5053,7 +5053,7 @@
           </x14:formula2>
           <xm:sqref>M20</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{26EF87F1-9D25-4E71-99D3-C228C0AD0ABA}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
+        <x14:dataValidation xr:uid="{24D52F3B-93E5-4154-A04D-A55F6843B748}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
           <x14:formula1>
             <xm:f>"Not Run,Pass,Fail,Blocked,Skipped"</xm:f>
           </x14:formula1>
@@ -5062,7 +5062,7 @@
           </x14:formula2>
           <xm:sqref>M21</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{46B6FE8D-85BF-4C62-A2BB-31E5587AF890}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
+        <x14:dataValidation xr:uid="{412ADD45-4CCF-4022-B95D-4C73F5B82CF2}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
           <x14:formula1>
             <xm:f>"Not Run,Pass,Fail,Blocked,Skipped"</xm:f>
           </x14:formula1>
@@ -5071,7 +5071,7 @@
           </x14:formula2>
           <xm:sqref>M23</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{4F431A2B-2B6C-4F38-BDA1-E79BD29CC40E}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
+        <x14:dataValidation xr:uid="{65667420-CC0D-4FCA-B6F9-F172EB96EA05}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
           <x14:formula1>
             <xm:f>"Not Run,Pass,Fail,Blocked,Skipped"</xm:f>
           </x14:formula1>
@@ -5080,7 +5080,7 @@
           </x14:formula2>
           <xm:sqref>M24</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{4D05FD78-F0B5-4334-8BE9-89F61249A41C}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
+        <x14:dataValidation xr:uid="{3D30BD1A-BF25-4BEA-8E6F-728FCEDAD285}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
           <x14:formula1>
             <xm:f>"Not Run,Pass,Fail,Blocked,Skipped"</xm:f>
           </x14:formula1>
@@ -5089,7 +5089,7 @@
           </x14:formula2>
           <xm:sqref>M25</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{7C9A1D03-7531-49DB-8965-ED0D4A458743}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
+        <x14:dataValidation xr:uid="{58F08322-8017-4C55-B344-74A1B86959E4}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
           <x14:formula1>
             <xm:f>"Not Run,Pass,Fail,Blocked,Skipped"</xm:f>
           </x14:formula1>
@@ -5212,7 +5212,7 @@
         <v>195</v>
       </c>
       <c r="M2" s="15" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N2" s="15"/>
       <c r="O2" s="15"/>
@@ -5255,7 +5255,7 @@
         <v>195</v>
       </c>
       <c r="M3" s="15" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N3" s="15"/>
       <c r="O3" s="15"/>
@@ -5298,7 +5298,7 @@
         <v>195</v>
       </c>
       <c r="M4" s="15" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N4" s="15"/>
       <c r="O4" s="15"/>
@@ -5341,7 +5341,7 @@
         <v>195</v>
       </c>
       <c r="M5" s="15" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N5" s="15"/>
       <c r="O5" s="15" t="s">
@@ -5386,7 +5386,7 @@
         <v>219</v>
       </c>
       <c r="M6" s="15" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N6" s="15"/>
       <c r="O6" s="15"/>
@@ -5429,7 +5429,7 @@
         <v>219</v>
       </c>
       <c r="M7" s="15" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N7" s="15"/>
       <c r="O7" s="15"/>
@@ -5472,7 +5472,7 @@
         <v>230</v>
       </c>
       <c r="M8" s="15" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N8" s="15"/>
       <c r="O8" s="15"/>
@@ -5515,7 +5515,7 @@
         <v>230</v>
       </c>
       <c r="M9" s="15" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N9" s="15"/>
       <c r="O9" s="15"/>
@@ -5558,7 +5558,7 @@
         <v>242</v>
       </c>
       <c r="M10" s="15" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N10" s="15"/>
       <c r="O10" s="15"/>
@@ -5601,7 +5601,7 @@
         <v>242</v>
       </c>
       <c r="M11" s="15" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N11" s="15"/>
       <c r="O11" s="15"/>
@@ -5644,7 +5644,7 @@
         <v>242</v>
       </c>
       <c r="M12" s="15" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N12" s="15"/>
       <c r="O12" s="15"/>
@@ -5687,7 +5687,7 @@
         <v>259</v>
       </c>
       <c r="M13" s="15" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N13" s="15"/>
       <c r="O13" s="15"/>
@@ -5730,7 +5730,7 @@
         <v>266</v>
       </c>
       <c r="M14" s="15" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N14" s="15"/>
       <c r="O14" s="15"/>
@@ -5773,7 +5773,7 @@
         <v>266</v>
       </c>
       <c r="M15" s="15" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N15" s="15"/>
       <c r="O15" s="15"/>
@@ -5816,7 +5816,7 @@
         <v>195</v>
       </c>
       <c r="M16" s="15" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N16" s="15"/>
       <c r="O16" s="15" t="s">
@@ -5861,7 +5861,7 @@
         <v>219</v>
       </c>
       <c r="M17" s="15" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N17" s="15"/>
       <c r="O17" s="15"/>
@@ -5904,7 +5904,7 @@
         <v>195</v>
       </c>
       <c r="M18" s="15" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N18" s="15"/>
       <c r="O18" s="15"/>
@@ -5947,7 +5947,7 @@
         <v>266</v>
       </c>
       <c r="M19" s="15" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N19" s="15"/>
       <c r="O19" s="15"/>
@@ -6017,15 +6017,153 @@
           </x14:cfRule>
           <xm:sqref>M2:M19</xm:sqref>
         </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Pass"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC6EFCE"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M15:M16</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Fail"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M15:M16</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Blocked"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFEB9C"/>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M15:M16</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Pass"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC6EFCE"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M17:M19</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Fail"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M17:M19</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Blocked"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFEB9C"/>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M17:M19</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Pass"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC6EFCE"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M17:M19</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Fail"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M17:M19</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
+            <xm:f>"Blocked"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFEB9C"/>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M17:M19</xm:sqref>
+        </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1" disablePrompts="0">
-        <x14:dataValidation xr:uid="{249AFDEA-C53C-44E5-B19A-4A3831F35E64}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3" disablePrompts="0">
+        <x14:dataValidation xr:uid="{523F2BC9-A78A-4AF6-95EB-35D661DC0BF7}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
           <x14:formula1>
             <xm:f>"Not Run,Pass,Fail,Blocked,Skipped"</xm:f>
           </x14:formula1>
-          <xm:sqref>M2:M19</xm:sqref>
+          <xm:sqref>M2:M14</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation xr:uid="{41A20C3C-8B84-4CF1-9E96-9528D1DC79EF}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
+          <x14:formula1>
+            <xm:f>"Not Run,Pass,Fail,Blocked,Skipped"</xm:f>
+          </x14:formula1>
+          <xm:sqref>M15:M16</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation xr:uid="{668078D8-A191-41E2-B1B4-75B364D4C617}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
+          <x14:formula1>
+            <xm:f>"Not Run,Pass,Fail,Blocked,Skipped"</xm:f>
+          </x14:formula1>
+          <xm:sqref>M17:M19</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -6784,7 +6922,7 @@
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1" disablePrompts="0">
-        <x14:dataValidation xr:uid="{3E07C439-6CF5-429E-A749-7899EFA7F43D}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
+        <x14:dataValidation xr:uid="{1BA9D181-C2EF-4231-9122-93ACF90C89AB}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
           <x14:formula1>
             <xm:f>"Not Run,Pass,Fail,Blocked,Skipped"</xm:f>
           </x14:formula1>
